--- a/outputs/week2_excel/920100_三协电机_三表抽取.xlsx
+++ b/outputs/week2_excel/920100_三协电机_三表抽取.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,11 +456,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2022-07-09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -475,17 +475,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2022年6月24日，公司召开第二届董事会第四次会议审议通过了《关于&lt;常州三协电机股份有限公司股票定向发行说明书&gt;的议案》。...本次股票发行价格为4.48元/股，共发行普通股530.00万股，募集资金总额为2,374.40万元。...截至2022年8月9日，公司已收到稳正景明、长泽创投缴纳的出资款2,374.40万元。</t>
+          <t>2022 年 7 月 9 日，常州三协电机股份有限公司 2022 年度第一次临时股东大会审议通过《关于&lt;常州三协电机股份有限公司股票定向发行说明书&gt;的议案》，公司向稳正景明和长泽创投定向发行股票，发行股数为530万股，每股认购价格为 4.48元/股。本次募集资金总额为2,374.40万元，以货币资金形式认缴，其中530.00 万元计入注册资本，1,844.40 万元增加资本公积。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2022-07-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,382 +500,36 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2022年6月24日，公司召开第二届董事会第四次会议审议通过了《关于&lt;常州三协电机股份有限公司股票定向发行说明书&gt;的议案》。...本次股票发行价格为4.48元/股，共发行普通股530.00万股，募集资金总额为2,374.40万元。...截至2022年8月9日，公司已收到稳正景明、长泽创投缴纳的出资款2,374.40万元。</t>
+          <t>2022 年 7 月 9 日，常州三协电机股份有限公司 2022 年度第一次临时股东大会审议通过《关于&lt;常州三协电机股份有限公司股票定向发行说明书&gt;的议案》，公司向稳正景明和长泽创投定向发行股票，发行股数为530万股，每股认购价格为 4.48元/股。本次募集资金总额为2,374.40万元，以货币资金形式认缴，其中530.00 万元计入注册资本，1,844.40 万元增加资本公积。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>盛祎</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>（未披露具体认购方名称）</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>318.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1723.09</v>
+      </c>
       <c r="F4" t="n">
         <v>5.41</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2023年5月26日，公司召开第二届董事会第十三次会议审议通过了《关于&lt;常州三协电机股份有限公司股票定向发行说明书&gt;的议案》。...本次股票拟发行价格为5.41元/股，拟发行普通股321.50万股，拟募集资金总额为1,739.32万元。...截至2023年9月6日，公司已收到盛祎、盛松、薛小丽、倪进宽、余方成、吴春扣、陆宇君、戈翔俊、陈都亮、圣利、董雪强、文涛、付荷庆、陈韵和盛月瑶15名认购人缴纳的出资款1,723.09万元。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>32</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>盛松</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2023年5月26日，公司召开第二届董事会第十三次会议审议通过了《关于&lt;常州三协电机股份有限公司股票定向发行说明书&gt;的议案》。...本次股票拟发行价格为5.41元/股，拟发行普通股321.50万股，拟募集资金总额为1,739.32万元。...截至2023年9月6日，公司已收到盛祎、盛松、薛小丽、倪进宽、余方成、吴春扣、陆宇君、戈翔俊、陈都亮、圣利、董雪强、文涛、付荷庆、陈韵和盛月瑶15名认购人缴纳的出资款1,723.09万元。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>薛小丽</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2023年5月26日，公司召开第二届董事会第十三次会议审议通过了《关于&lt;常州三协电机股份有限公司股票定向发行说明书&gt;的议案》。...本次股票拟发行价格为5.41元/股，拟发行普通股321.50万股，拟募集资金总额为1,739.32万元。...截至2023年9月6日，公司已收到盛祎、盛松、薛小丽、倪进宽、余方成、吴春扣、陆宇君、戈翔俊、陈都亮、圣利、董雪强、文涛、付荷庆、陈韵和盛月瑶15名认购人缴纳的出资款1,723.09万元。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>倪进宽</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2023年5月26日，公司召开第二届董事会第十三次会议审议通过了《关于&lt;常州三协电机股份有限公司股票定向发行说明书&gt;的议案》。...本次股票拟发行价格为5.41元/股，拟发行普通股321.50万股，拟募集资金总额为1,739.32万元。...截至2023年9月6日，公司已收到盛祎、盛松、薛小丽、倪进宽、余方成、吴春扣、陆宇君、戈翔俊、陈都亮、圣利、董雪强、文涛、付荷庆、陈韵和盛月瑶15名认购人缴纳的出资款1,723.09万元。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>32</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>余方成</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2023年5月26日，公司召开第二届董事会第十三次会议审议通过了《关于&lt;常州三协电机股份有限公司股票定向发行说明书&gt;的议案》。...本次股票拟发行价格为5.41元/股，拟发行普通股321.50万股，拟募集资金总额为1,739.32万元。...截至2023年9月6日，公司已收到盛祎、盛松、薛小丽、倪进宽、余方成、吴春扣、陆宇君、戈翔俊、陈都亮、圣利、董雪强、文涛、付荷庆、陈韵和盛月瑶15名认购人缴纳的出资款1,723.09万元。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>32</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>吴春扣</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2023年5月26日，公司召开第二届董事会第十三次会议审议通过了《关于&lt;常州三协电机股份有限公司股票定向发行说明书&gt;的议案》。...本次股票拟发行价格为5.41元/股，拟发行普通股321.50万股，拟募集资金总额为1,739.32万元。...截至2023年9月6日，公司已收到盛祎、盛松、薛小丽、倪进宽、余方成、吴春扣、陆宇君、戈翔俊、陈都亮、圣利、董雪强、文涛、付荷庆、陈韵和盛月瑶15名认购人缴纳的出资款1,723.09万元。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>32</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>陆宇君</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2023年5月26日，公司召开第二届董事会第十三次会议审议通过了《关于&lt;常州三协电机股份有限公司股票定向发行说明书&gt;的议案》。...本次股票拟发行价格为5.41元/股，拟发行普通股321.50万股，拟募集资金总额为1,739.32万元。...截至2023年9月6日，公司已收到盛祎、盛松、薛小丽、倪进宽、余方成、吴春扣、陆宇君、戈翔俊、陈都亮、圣利、董雪强、文涛、付荷庆、陈韵和盛月瑶15名认购人缴纳的出资款1,723.09万元。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>32</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>戈翔俊</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2023年5月26日，公司召开第二届董事会第十三次会议审议通过了《关于&lt;常州三协电机股份有限公司股票定向发行说明书&gt;的议案》。...本次股票拟发行价格为5.41元/股，拟发行普通股321.50万股，拟募集资金总额为1,739.32万元。...截至2023年9月6日，公司已收到盛祎、盛松、薛小丽、倪进宽、余方成、吴春扣、陆宇君、戈翔俊、陈都亮、圣利、董雪强、文涛、付荷庆、陈韵和盛月瑶15名认购人缴纳的出资款1,723.09万元。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>32</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>陈都亮</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2023年5月26日，公司召开第二届董事会第十三次会议审议通过了《关于&lt;常州三协电机股份有限公司股票定向发行说明书&gt;的议案》。...本次股票拟发行价格为5.41元/股，拟发行普通股321.50万股，拟募集资金总额为1,739.32万元。...截至2023年9月6日，公司已收到盛祎、盛松、薛小丽、倪进宽、余方成、吴春扣、陆宇君、戈翔俊、陈都亮、圣利、董雪强、文涛、付荷庆、陈韵和盛月瑶15名认购人缴纳的出资款1,723.09万元。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>32</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>圣利</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2023年5月26日，公司召开第二届董事会第十三次会议审议通过了《关于&lt;常州三协电机股份有限公司股票定向发行说明书&gt;的议案》。...本次股票拟发行价格为5.41元/股，拟发行普通股321.50万股，拟募集资金总额为1,739.32万元。...截至2023年9月6日，公司已收到盛祎、盛松、薛小丽、倪进宽、余方成、吴春扣、陆宇君、戈翔俊、陈都亮、圣利、董雪强、文涛、付荷庆、陈韵和盛月瑶15名认购人缴纳的出资款1,723.09万元。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>32</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>董雪强</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2023年5月26日，公司召开第二届董事会第十三次会议审议通过了《关于&lt;常州三协电机股份有限公司股票定向发行说明书&gt;的议案》。...本次股票拟发行价格为5.41元/股，拟发行普通股321.50万股，拟募集资金总额为1,739.32万元。...截至2023年9月6日，公司已收到盛祎、盛松、薛小丽、倪进宽、余方成、吴春扣、陆宇君、戈翔俊、陈都亮、圣利、董雪强、文涛、付荷庆、陈韵和盛月瑶15名认购人缴纳的出资款1,723.09万元。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>32</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>文涛</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2023年5月26日，公司召开第二届董事会第十三次会议审议通过了《关于&lt;常州三协电机股份有限公司股票定向发行说明书&gt;的议案》。...本次股票拟发行价格为5.41元/股，拟发行普通股321.50万股，拟募集资金总额为1,739.32万元。...截至2023年9月6日，公司已收到盛祎、盛松、薛小丽、倪进宽、余方成、吴春扣、陆宇君、戈翔俊、陈都亮、圣利、董雪强、文涛、付荷庆、陈韵和盛月瑶15名认购人缴纳的出资款1,723.09万元。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>32</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>付荷庆</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2023年5月26日，公司召开第二届董事会第十三次会议审议通过了《关于&lt;常州三协电机股份有限公司股票定向发行说明书&gt;的议案》。...本次股票拟发行价格为5.41元/股，拟发行普通股321.50万股，拟募集资金总额为1,739.32万元。...截至2023年9月6日，公司已收到盛祎、盛松、薛小丽、倪进宽、余方成、吴春扣、陆宇君、戈翔俊、陈都亮、圣利、董雪强、文涛、付荷庆、陈韵和盛月瑶15名认购人缴纳的出资款1,723.09万元。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>32</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>陈韵</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2023年5月26日，公司召开第二届董事会第十三次会议审议通过了《关于&lt;常州三协电机股份有限公司股票定向发行说明书&gt;的议案》。...本次股票拟发行价格为5.41元/股，拟发行普通股321.50万股，拟募集资金总额为1,739.32万元。...截至2023年9月6日，公司已收到盛祎、盛松、薛小丽、倪进宽、余方成、吴春扣、陆宇君、戈翔俊、陈都亮、圣利、董雪强、文涛、付荷庆、陈韵和盛月瑶15名认购人缴纳的出资款1,723.09万元。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>32</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>盛月瑶</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2023年5月26日，公司召开第二届董事会第十三次会议审议通过了《关于&lt;常州三协电机股份有限公司股票定向发行说明书&gt;的议案》。...本次股票拟发行价格为5.41元/股，拟发行普通股321.50万股，拟募集资金总额为1,739.32万元。...截至2023年9月6日，公司已收到盛祎、盛松、薛小丽、倪进宽、余方成、吴春扣、陆宇君、戈翔俊、陈都亮、圣利、董雪强、文涛、付荷庆、陈韵和盛月瑶15名认购人缴纳的出资款1,723.09万元。</t>
+          <t>2023年 8月 28日，公司实际发行 318.5 万股，增发价格为 5.41 元/股，全部以货币资金形式认缴，实际募集资金总额为 1,723.09万元，其中318.5万元计入股本，1,404.59万元计入资本公积，本次发行完成后公司股本总额增至3,848.50万元，由苏亚金诚审验，于 2023年 9月 8 日出具苏亚验[2023]10号验资报告。</t>
         </is>
       </c>
     </row>
@@ -890,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -947,7 +601,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -956,50 +610,48 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>本次发行前公司股权结构（报告期初或最早可识别结构）</t>
+          <t>2022年7月增资前股权结构（报告期初）</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5310.93</v>
+        <v>3000</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>盛祎</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>3344.44</v>
-      </c>
+          <t>（未披露具体股东名称）</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>本次发行前，公司总股本为5,310.93万股...截至本招股说明书签署日，发行人控股股东为盛祎，直接持有发行人股份3,344.44万股，持股比例为62.97%。</t>
+          <t>本次发行完成后公司注册资本为3,530.00万元（注：增资前注册资本为3000万元，由增资530万股推算）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>t0</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>本次发行前公司股权结构（报告期初或最早可识别结构）</t>
+          <t>2022年7月增资后股权结构</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5310.93</v>
+        <v>3530</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>朱绶青</t>
+          <t>稳正景明</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -1007,41 +659,103 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>朱绶青直接持有发行人19.49%的股份。</t>
+          <t>本次发行完成后公司注册资本为3,530.00万元，并由苏亚金诚于 2022年 8月 15日出具苏亚锡验[2022]第7号《验资报告》。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>t0</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>本次发行前公司股权结构（报告期初或最早可识别结构）</t>
+          <t>2022年7月增资后股权结构</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5310.93</v>
+        <v>3530</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>稳正景明</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>486.7</v>
-      </c>
+          <t>长泽创投</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>持有公司5%以上股份的其他主要股东为稳正景明，持有数量为486.70万股，持股比例为9.16%</t>
+          <t>本次发行完成后公司注册资本为3,530.00万元，并由苏亚金诚于 2022年 8月 15日出具苏亚锡验[2022]第7号《验资报告》。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2023年8月增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3848.5</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>（未披露具体股东名称）</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>本次发行完成后公司股本总额增至3,848.50万元，由苏亚金诚审验，于 2023年 9月 8 日出具苏亚验[2023]10号验资报告。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>53</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2023年12月权益分派后股权结构</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5310.93</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>（未披露具体股东名称）</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>分红前公司总股本为 3,848.50万股，分红后总股本增至5,310.93万股，合计增加 1,462.43万股。</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/920100_三协电机_三表抽取.xlsx
+++ b/outputs/week2_excel/920100_三协电机_三表抽取.xlsx
@@ -468,8 +468,12 @@
           <t>稳正景明</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>265</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1187.2</v>
+      </c>
       <c r="F2" t="n">
         <v>4.48</v>
       </c>
@@ -493,8 +497,12 @@
           <t>长泽创投</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>265</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1187.2</v>
+      </c>
       <c r="F3" t="n">
         <v>4.48</v>
       </c>
@@ -637,21 +645,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>t0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2022年7月增资后股权结构</t>
+          <t>2022年7月增资前股权结构（报告期初）</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3530</v>
+        <v>3000</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>稳正景明</t>
+          <t>（未披露具体股东名称）</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -659,7 +667,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>本次发行完成后公司注册资本为3,530.00万元，并由苏亚金诚于 2022年 8月 15日出具苏亚锡验[2022]第7号《验资报告》。</t>
+          <t>本次发行完成后公司注册资本为3,530.00万元（注：增资前注册资本为3000万元，由增资530万股推算）</t>
         </is>
       </c>
     </row>
@@ -669,21 +677,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>t0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2022年7月增资后股权结构</t>
+          <t>2022年7月增资前股权结构（报告期初）</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3530</v>
+        <v>3000</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>长泽创投</t>
+          <t>（未披露具体股东名称）</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -691,7 +699,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>本次发行完成后公司注册资本为3,530.00万元，并由苏亚金诚于 2022年 8月 15日出具苏亚锡验[2022]第7号《验资报告》。</t>
+          <t>本次发行完成后公司注册资本为3,530.00万元（注：增资前注册资本为3000万元，由增资530万股推算）</t>
         </is>
       </c>
     </row>
@@ -701,16 +709,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2023年8月增资后股权结构</t>
+          <t>2022年7月增资前股权结构（报告期初）</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3848.5</v>
+        <v>3000</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
@@ -723,7 +731,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>本次发行完成后公司股本总额增至3,848.50万元，由苏亚金诚审验，于 2023年 9月 8 日出具苏亚验[2023]10号验资报告。</t>
+          <t>本次发行完成后公司注册资本为3,530.00万元（注：增资前注册资本为3000万元，由增资530万股推算）</t>
         </is>
       </c>
     </row>
@@ -733,16 +741,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>t0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2023年12月权益分派后股权结构</t>
+          <t>2022年7月增资前股权结构（报告期初）</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5310.93</v>
+        <v>3000</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
@@ -755,7 +763,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>分红前公司总股本为 3,848.50万股，分红后总股本增至5,310.93万股，合计增加 1,462.43万股。</t>
+          <t>本次发行完成后公司注册资本为3,530.00万元（注：增资前注册资本为3000万元，由增资530万股推算）</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/920100_三协电机_三表抽取.xlsx
+++ b/outputs/week2_excel/920100_三协电机_三表抽取.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,7 +609,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -618,152 +618,28 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2022年7月增资前股权结构（报告期初）</t>
+          <t>发行前（第34-35页）</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3000</v>
+        <v>5310.93</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>（未披露具体股东名称）</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>稳正景明</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>486.7</v>
+      </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>9.16</v>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>本次发行完成后公司注册资本为3,530.00万元（注：增资前注册资本为3000万元，由增资530万股推算）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>53</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>t0</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2022年7月增资前股权结构（报告期初）</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>（未披露具体股东名称）</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>本次发行完成后公司注册资本为3,530.00万元（注：增资前注册资本为3000万元，由增资530万股推算）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>53</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>t0</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2022年7月增资前股权结构（报告期初）</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>（未披露具体股东名称）</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>本次发行完成后公司注册资本为3,530.00万元（注：增资前注册资本为3000万元，由增资530万股推算）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>53</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>t0</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2022年7月增资前股权结构（报告期初）</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>（未披露具体股东名称）</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>本次发行完成后公司注册资本为3,530.00万元（注：增资前注册资本为3000万元，由增资530万股推算）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>53</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>t0</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2022年7月增资前股权结构（报告期初）</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>（未披露具体股东名称）</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>本次发行完成后公司注册资本为3,530.00万元（注：增资前注册资本为3000万元，由增资530万股推算）</t>
+          <t>持有公司 5%以上股份的其他主要股东为稳正景明，持有数量为 486.70万股，持股比例为9.16%</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/920100_三协电机_三表抽取.xlsx
+++ b/outputs/week2_excel/920100_三协电机_三表抽取.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,7 +609,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -618,28 +618,1250 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>发行前（第34-35页）</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>5310.93</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>2019年5月深圳三协设立时股权结构</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>300</v>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>稳正景明</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>486.7</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="n">
-        <v>9.16</v>
-      </c>
+          <t>德智高新</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>153</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>持有公司 5%以上股份的其他主要股东为稳正景明，持有数量为 486.70万股，持股比例为9.16%</t>
+          <t>2019年 5月15日，德智高新、陆宇君、陈广武共同签署《深圳市三协电机有限公司公司章程》，设立深圳三协，注册资本为人民币 300.00万元。其中，德智高新持有 51%的股权，陆宇君持有 29%的股权，陈广武持有20%的股权。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>43</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>t0</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2019年5月深圳三协设立时股权结构</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>300</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>陆宇君</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>87</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2019年 5月15日，德智高新、陆宇君、陈广武共同签署《深圳市三协电机有限公司公司章程》，设立深圳三协，注册资本为人民币 300.00万元。其中，德智高新持有 51%的股权，陆宇君持有 29%的股权，陈广武持有20%的股权。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>43</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>t0</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2019年5月深圳三协设立时股权结构</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>300</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>60</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2019年 5月15日，德智高新、陆宇君、陈广武共同签署《深圳市三协电机有限公司公司章程》，设立深圳三协，注册资本为人民币 300.00万元。其中，德智高新持有 51%的股权，陆宇君持有 29%的股权，陈广武持有20%的股权。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2019年7月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>300</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>153</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2019年 7月18日，深圳三协召开股东会，作出决议，同意股东德智高新将其所持公司 51%的股权转让给朱南保。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>44</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2019年7月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>300</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>陆宇君</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>87</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2019年 7月18日，深圳三协召开股东会，作出决议，同意股东德智高新将其所持公司 51%的股权转让给朱南保。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2019年7月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>300</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>60</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2019年 7月18日，深圳三协召开股东会，作出决议，同意股东德智高新将其所持公司 51%的股权转让给朱南保。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>44</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2019年12月/2020年1月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>300</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>90</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2019年 12月 4日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21%的股权转让给卢娇娇；同意股东陈广武将其所持公司4%的股权转让给卢娇娇；同意股东陈广武将其所持公司6%的股权转让给陆宇君。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>44</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2019年12月/2020年1月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>300</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>陆宇君</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>105</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2019年 12月 4日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21%的股权转让给卢娇娇；同意股东陈广武将其所持公司4%的股权转让给卢娇娇；同意股东陈广武将其所持公司6%的股权转让给陆宇君。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2019年12月/2020年1月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>300</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>卢娇娇</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>75</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2019年 12月 4日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21%的股权转让给卢娇娇；同意股东陈广武将其所持公司4%的股权转让给卢娇娇；同意股东陈广武将其所持公司6%的股权转让给陆宇君。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>44</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2019年12月/2020年1月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>300</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2019年 12月 4日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21%的股权转让给卢娇娇；同意股东陈广武将其所持公司4%的股权转让给卢娇娇；同意股东陈广武将其所持公司6%的股权转让给陆宇君。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>45</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2021年5月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>300</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>75</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意股东卢娇娇将其所持公司 25%的股权转让给王洪波；同意股东朱南保将其所占公司5%的股权转让给王洪波；同意股东陈广武将其所占公司2.5%的股权转让给王洪波。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>45</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2021年5月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>300</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>陆宇君</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>105</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意股东卢娇娇将其所持公司 25%的股权转让给王洪波；同意股东朱南保将其所占公司5%的股权转让给王洪波；同意股东陈广武将其所占公司2.5%的股权转让给王洪波。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>45</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2021年5月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>300</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>王洪波</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意股东卢娇娇将其所持公司 25%的股权转让给王洪波；同意股东朱南保将其所占公司5%的股权转让给王洪波；同意股东陈广武将其所占公司2.5%的股权转让给王洪波。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>45</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2021年5月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>300</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意股东卢娇娇将其所持公司 25%的股权转让给王洪波；同意股东朱南保将其所占公司5%的股权转让给王洪波；同意股东陈广武将其所占公司2.5%的股权转让给王洪波。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>45</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2021年5月增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>400</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>85</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意增加注册资本 100万元，即由原来 300 万元增加至400万元，由原股东同比例增资。其中，股东朱南保增加出资10 万元，股东陆宇君增加出资35万元，股东王洪波增加出资 55 万元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>45</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2021年5月增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>400</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>陆宇君</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>140</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意增加注册资本 100万元，即由原来 300 万元增加至400万元，由原股东同比例增资。其中，股东朱南保增加出资10 万元，股东陆宇君增加出资35万元，股东王洪波增加出资 55 万元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>45</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2021年5月增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>400</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>王洪波</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意增加注册资本 100万元，即由原来 300 万元增加至400万元，由原股东同比例增资。其中，股东朱南保增加出资10 万元，股东陆宇君增加出资35万元，股东王洪波增加出资 55 万元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>45</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2021年5月增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>400</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意增加注册资本 100万元，即由原来 300 万元增加至400万元，由原股东同比例增资。其中，股东朱南保增加出资10 万元，股东陆宇君增加出资35万元，股东王洪波增加出资 55 万元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>45</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2022年10月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>400</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>225</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2022年 10月 19日，深圳三协召开股东会，作出决议，同意股东陆宇君将其持有公司 35%的股权转让给朱南保。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>45</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2022年10月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>400</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>王洪波</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2022年 10月 19日，深圳三协召开股东会，作出决议，同意股东陆宇君将其持有公司 35%的股权转让给朱南保。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>45</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2022年10月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>400</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2022年 10月 19日，深圳三协召开股东会，作出决议，同意股东陆宇君将其持有公司 35%的股权转让给朱南保。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>46</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2022年11月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>400</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="n">
+        <v>225</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2022年 10月 26日，深圳三协召开股东会，作出决议，同意股东王洪波将其所持公司 32.5%的股权转让给发行人全资子公司三合融创。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>46</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2022年11月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>400</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>三合融创</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>130</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2022年 10月 26日，深圳三协召开股东会，作出决议，同意股东王洪波将其所持公司 32.5%的股权转让给发行人全资子公司三合融创。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>46</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2022年11月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>400</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2022年 10月 26日，深圳三协召开股东会，作出决议，同意股东王洪波将其所持公司 32.5%的股权转让给发行人全资子公司三合融创。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>46</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>t7</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2023年3月增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>440</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="n">
+        <v>225</v>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2023年 3月30日，深圳三协召开股东会，全体股东一致同意将原注册资本 400万元变更为 440万元，由新股东黄晓彬认缴新增注册资本40万元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>46</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>t7</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2023年3月增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>440</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>三合融创</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>130</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2023年 3月30日，深圳三协召开股东会，全体股东一致同意将原注册资本 400万元变更为 440万元，由新股东黄晓彬认缴新增注册资本40万元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>46</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>t7</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2023年3月增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>440</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2023年 3月30日，深圳三协召开股东会，全体股东一致同意将原注册资本 400万元变更为 440万元，由新股东黄晓彬认缴新增注册资本40万元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>46</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>t7</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2023年3月增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>440</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>黄晓彬</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>40</v>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2023年 3月30日，深圳三协召开股东会，全体股东一致同意将原注册资本 400万元变更为 440万元，由新股东黄晓彬认缴新增注册资本40万元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>46</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>t8</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2023年8月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>440</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>三合融创</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2023年 8月21日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21.46%的股权转让给三合融创。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>46</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>t8</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2023年8月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>440</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>130.576</v>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2023年 8月21日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21.46%的股权转让给三合融创。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>46</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>t8</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2023年8月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>440</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2023年 8月21日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21.46%的股权转让给三合融创。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>46</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>t8</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2023年8月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>440</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>黄晓彬</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="n">
+        <v>40</v>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2023年 8月21日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21.46%的股权转让给三合融创。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>47</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>t9</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2024年6月减资后股权结构</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="n">
+        <v>400</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>三合融创</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2024年 3月1日，深圳三协召开股东会，决定深圳三协注册资本由人民币 440.00万元减少至人民币400.00万元，减资后的股东变更为三合融创、朱南保、陈广武，并修改章程相应条款。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>47</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>t9</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2024年6月减资后股权结构</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>400</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="n">
+        <v>130.576</v>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2024年 3月1日，深圳三协召开股东会，决定深圳三协注册资本由人民币 440.00万元减少至人民币400.00万元，减资后的股东变更为三合融创、朱南保、陈广武，并修改章程相应条款。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>47</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>t9</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2024年6月减资后股权结构</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>400</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2024年 3月1日，深圳三协召开股东会，决定深圳三协注册资本由人民币 440.00万元减少至人民币400.00万元，减资后的股东变更为三合融创、朱南保、陈广武，并修改章程相应条款。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>47</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>t10</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2025年7月减资后股权结构</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="n">
+        <v>370</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>三合融创</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2025年 3月25日，深圳三协召开股东会，决定深圳三协注册资本由人民币400.00万元减少至人民币370.00万元，减资后的股东变更为三合融创、朱南保，并修改章程相应条款。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>47</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>t10</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2025年7月减资后股权结构</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="n">
+        <v>370</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="n">
+        <v>130.576</v>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2025年 3月25日，深圳三协召开股东会，决定深圳三协注册资本由人民币400.00万元减少至人民币370.00万元，减资后的股东变更为三合融创、朱南保，并修改章程相应条款。</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/920100_三协电机_三表抽取.xlsx
+++ b/outputs/week2_excel/920100_三协电机_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -621,7 +622,6 @@
           <t>2019年5月深圳三协设立时股权结构</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>300</v>
       </c>
@@ -630,11 +630,9 @@
           <t>德智高新</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>153</v>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>2019年 5月15日，德智高新、陆宇君、陈广武共同签署《深圳市三协电机有限公司公司章程》，设立深圳三协，注册资本为人民币 300.00万元。其中，德智高新持有 51%的股权，陆宇君持有 29%的股权，陈广武持有20%的股权。</t>
@@ -655,7 +653,6 @@
           <t>2019年5月深圳三协设立时股权结构</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>300</v>
       </c>
@@ -664,11 +661,9 @@
           <t>陆宇君</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>87</v>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>2019年 5月15日，德智高新、陆宇君、陈广武共同签署《深圳市三协电机有限公司公司章程》，设立深圳三协，注册资本为人民币 300.00万元。其中，德智高新持有 51%的股权，陆宇君持有 29%的股权，陈广武持有20%的股权。</t>
@@ -689,7 +684,6 @@
           <t>2019年5月深圳三协设立时股权结构</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>300</v>
       </c>
@@ -698,11 +692,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>60</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>2019年 5月15日，德智高新、陆宇君、陈广武共同签署《深圳市三协电机有限公司公司章程》，设立深圳三协，注册资本为人民币 300.00万元。其中，德智高新持有 51%的股权，陆宇君持有 29%的股权，陈广武持有20%的股权。</t>
@@ -723,7 +715,6 @@
           <t>2019年7月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>300</v>
       </c>
@@ -732,11 +723,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>153</v>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>2019年 7月18日，深圳三协召开股东会，作出决议，同意股东德智高新将其所持公司 51%的股权转让给朱南保。</t>
@@ -757,7 +746,6 @@
           <t>2019年7月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
         <v>300</v>
       </c>
@@ -766,11 +754,9 @@
           <t>陆宇君</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>87</v>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>2019年 7月18日，深圳三协召开股东会，作出决议，同意股东德智高新将其所持公司 51%的股权转让给朱南保。</t>
@@ -791,7 +777,6 @@
           <t>2019年7月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
         <v>300</v>
       </c>
@@ -800,11 +785,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>60</v>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>2019年 7月18日，深圳三协召开股东会，作出决议，同意股东德智高新将其所持公司 51%的股权转让给朱南保。</t>
@@ -825,7 +808,6 @@
           <t>2019年12月/2020年1月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
         <v>300</v>
       </c>
@@ -834,11 +816,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>90</v>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>2019年 12月 4日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21%的股权转让给卢娇娇；同意股东陈广武将其所持公司4%的股权转让给卢娇娇；同意股东陈广武将其所持公司6%的股权转让给陆宇君。</t>
@@ -859,7 +839,6 @@
           <t>2019年12月/2020年1月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
         <v>300</v>
       </c>
@@ -868,11 +847,9 @@
           <t>陆宇君</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>105</v>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>2019年 12月 4日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21%的股权转让给卢娇娇；同意股东陈广武将其所持公司4%的股权转让给卢娇娇；同意股东陈广武将其所持公司6%的股权转让给陆宇君。</t>
@@ -893,7 +870,6 @@
           <t>2019年12月/2020年1月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
         <v>300</v>
       </c>
@@ -902,11 +878,9 @@
           <t>卢娇娇</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>75</v>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>2019年 12月 4日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21%的股权转让给卢娇娇；同意股东陈广武将其所持公司4%的股权转让给卢娇娇；同意股东陈广武将其所持公司6%的股权转让给陆宇君。</t>
@@ -927,7 +901,6 @@
           <t>2019年12月/2020年1月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
         <v>300</v>
       </c>
@@ -936,11 +909,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>30</v>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>2019年 12月 4日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21%的股权转让给卢娇娇；同意股东陈广武将其所持公司4%的股权转让给卢娇娇；同意股东陈广武将其所持公司6%的股权转让给陆宇君。</t>
@@ -961,7 +932,6 @@
           <t>2021年5月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
         <v>300</v>
       </c>
@@ -970,11 +940,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>75</v>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意股东卢娇娇将其所持公司 25%的股权转让给王洪波；同意股东朱南保将其所占公司5%的股权转让给王洪波；同意股东陈广武将其所占公司2.5%的股权转让给王洪波。</t>
@@ -995,7 +963,6 @@
           <t>2021年5月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
         <v>300</v>
       </c>
@@ -1004,11 +971,9 @@
           <t>陆宇君</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>105</v>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意股东卢娇娇将其所持公司 25%的股权转让给王洪波；同意股东朱南保将其所占公司5%的股权转让给王洪波；同意股东陈广武将其所占公司2.5%的股权转让给王洪波。</t>
@@ -1029,7 +994,6 @@
           <t>2021年5月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
         <v>300</v>
       </c>
@@ -1038,11 +1002,9 @@
           <t>王洪波</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>97.5</v>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意股东卢娇娇将其所持公司 25%的股权转让给王洪波；同意股东朱南保将其所占公司5%的股权转让给王洪波；同意股东陈广武将其所占公司2.5%的股权转让给王洪波。</t>
@@ -1063,7 +1025,6 @@
           <t>2021年5月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
         <v>300</v>
       </c>
@@ -1072,11 +1033,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>22.5</v>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意股东卢娇娇将其所持公司 25%的股权转让给王洪波；同意股东朱南保将其所占公司5%的股权转让给王洪波；同意股东陈广武将其所占公司2.5%的股权转让给王洪波。</t>
@@ -1097,7 +1056,6 @@
           <t>2021年5月增资后股权结构</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
         <v>400</v>
       </c>
@@ -1106,11 +1064,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>85</v>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意增加注册资本 100万元，即由原来 300 万元增加至400万元，由原股东同比例增资。其中，股东朱南保增加出资10 万元，股东陆宇君增加出资35万元，股东王洪波增加出资 55 万元。</t>
@@ -1131,7 +1087,6 @@
           <t>2021年5月增资后股权结构</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
         <v>400</v>
       </c>
@@ -1140,11 +1095,9 @@
           <t>陆宇君</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>140</v>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意增加注册资本 100万元，即由原来 300 万元增加至400万元，由原股东同比例增资。其中，股东朱南保增加出资10 万元，股东陆宇君增加出资35万元，股东王洪波增加出资 55 万元。</t>
@@ -1165,7 +1118,6 @@
           <t>2021年5月增资后股权结构</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
         <v>400</v>
       </c>
@@ -1174,11 +1126,9 @@
           <t>王洪波</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>152.5</v>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意增加注册资本 100万元，即由原来 300 万元增加至400万元，由原股东同比例增资。其中，股东朱南保增加出资10 万元，股东陆宇君增加出资35万元，股东王洪波增加出资 55 万元。</t>
@@ -1199,7 +1149,6 @@
           <t>2021年5月增资后股权结构</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
         <v>400</v>
       </c>
@@ -1208,11 +1157,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>22.5</v>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意增加注册资本 100万元，即由原来 300 万元增加至400万元，由原股东同比例增资。其中，股东朱南保增加出资10 万元，股东陆宇君增加出资35万元，股东王洪波增加出资 55 万元。</t>
@@ -1233,7 +1180,6 @@
           <t>2022年10月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
         <v>400</v>
       </c>
@@ -1242,11 +1188,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>225</v>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>2022年 10月 19日，深圳三协召开股东会，作出决议，同意股东陆宇君将其持有公司 35%的股权转让给朱南保。</t>
@@ -1267,7 +1211,6 @@
           <t>2022年10月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
         <v>400</v>
       </c>
@@ -1276,11 +1219,9 @@
           <t>王洪波</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>152.5</v>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>2022年 10月 19日，深圳三协召开股东会，作出决议，同意股东陆宇君将其持有公司 35%的股权转让给朱南保。</t>
@@ -1301,7 +1242,6 @@
           <t>2022年10月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
         <v>400</v>
       </c>
@@ -1310,11 +1250,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>22.5</v>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>2022年 10月 19日，深圳三协召开股东会，作出决议，同意股东陆宇君将其持有公司 35%的股权转让给朱南保。</t>
@@ -1335,7 +1273,6 @@
           <t>2022年11月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
         <v>400</v>
       </c>
@@ -1344,11 +1281,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>225</v>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>2022年 10月 26日，深圳三协召开股东会，作出决议，同意股东王洪波将其所持公司 32.5%的股权转让给发行人全资子公司三合融创。</t>
@@ -1369,7 +1304,6 @@
           <t>2022年11月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
         <v>400</v>
       </c>
@@ -1378,11 +1312,9 @@
           <t>三合融创</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>130</v>
       </c>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>2022年 10月 26日，深圳三协召开股东会，作出决议，同意股东王洪波将其所持公司 32.5%的股权转让给发行人全资子公司三合融创。</t>
@@ -1403,7 +1335,6 @@
           <t>2022年11月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
         <v>400</v>
       </c>
@@ -1412,11 +1343,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>22.5</v>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>2022年 10月 26日，深圳三协召开股东会，作出决议，同意股东王洪波将其所持公司 32.5%的股权转让给发行人全资子公司三合融创。</t>
@@ -1437,7 +1366,6 @@
           <t>2023年3月增资后股权结构</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
         <v>440</v>
       </c>
@@ -1446,11 +1374,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>225</v>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>2023年 3月30日，深圳三协召开股东会，全体股东一致同意将原注册资本 400万元变更为 440万元，由新股东黄晓彬认缴新增注册资本40万元。</t>
@@ -1471,7 +1397,6 @@
           <t>2023年3月增资后股权结构</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
         <v>440</v>
       </c>
@@ -1480,11 +1405,9 @@
           <t>三合融创</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>130</v>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>2023年 3月30日，深圳三协召开股东会，全体股东一致同意将原注册资本 400万元变更为 440万元，由新股东黄晓彬认缴新增注册资本40万元。</t>
@@ -1505,7 +1428,6 @@
           <t>2023年3月增资后股权结构</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
         <v>440</v>
       </c>
@@ -1514,11 +1436,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>22.5</v>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>2023年 3月30日，深圳三协召开股东会，全体股东一致同意将原注册资本 400万元变更为 440万元，由新股东黄晓彬认缴新增注册资本40万元。</t>
@@ -1539,7 +1459,6 @@
           <t>2023年3月增资后股权结构</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
         <v>440</v>
       </c>
@@ -1548,11 +1467,9 @@
           <t>黄晓彬</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>40</v>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>2023年 3月30日，深圳三协召开股东会，全体股东一致同意将原注册资本 400万元变更为 440万元，由新股东黄晓彬认缴新增注册资本40万元。</t>
@@ -1573,7 +1490,6 @@
           <t>2023年8月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
         <v>440</v>
       </c>
@@ -1582,11 +1498,9 @@
           <t>三合融创</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>224.424</v>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>2023年 8月21日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21.46%的股权转让给三合融创。</t>
@@ -1607,7 +1521,6 @@
           <t>2023年8月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
         <v>440</v>
       </c>
@@ -1616,11 +1529,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>130.576</v>
       </c>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>2023年 8月21日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21.46%的股权转让给三合融创。</t>
@@ -1641,7 +1552,6 @@
           <t>2023年8月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
         <v>440</v>
       </c>
@@ -1650,11 +1560,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>22.5</v>
       </c>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>2023年 8月21日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21.46%的股权转让给三合融创。</t>
@@ -1675,7 +1583,6 @@
           <t>2023年8月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
         <v>440</v>
       </c>
@@ -1684,11 +1591,9 @@
           <t>黄晓彬</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>40</v>
       </c>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>2023年 8月21日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21.46%的股权转让给三合融创。</t>
@@ -1709,7 +1614,6 @@
           <t>2024年6月减资后股权结构</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
         <v>400</v>
       </c>
@@ -1718,11 +1622,9 @@
           <t>三合融创</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>224.424</v>
       </c>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>2024年 3月1日，深圳三协召开股东会，决定深圳三协注册资本由人民币 440.00万元减少至人民币400.00万元，减资后的股东变更为三合融创、朱南保、陈广武，并修改章程相应条款。</t>
@@ -1743,7 +1645,6 @@
           <t>2024年6月减资后股权结构</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
         <v>400</v>
       </c>
@@ -1752,11 +1653,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>130.576</v>
       </c>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>2024年 3月1日，深圳三协召开股东会，决定深圳三协注册资本由人民币 440.00万元减少至人民币400.00万元，减资后的股东变更为三合融创、朱南保、陈广武，并修改章程相应条款。</t>
@@ -1777,7 +1676,6 @@
           <t>2024年6月减资后股权结构</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
         <v>400</v>
       </c>
@@ -1786,11 +1684,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>22.5</v>
       </c>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>2024年 3月1日，深圳三协召开股东会，决定深圳三协注册资本由人民币 440.00万元减少至人民币400.00万元，减资后的股东变更为三合融创、朱南保、陈广武，并修改章程相应条款。</t>
@@ -1811,7 +1707,6 @@
           <t>2025年7月减资后股权结构</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
         <v>370</v>
       </c>
@@ -1820,11 +1715,9 @@
           <t>三合融创</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>224.424</v>
       </c>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>2025年 3月25日，深圳三协召开股东会，决定深圳三协注册资本由人民币400.00万元减少至人民币370.00万元，减资后的股东变更为三合融创、朱南保，并修改章程相应条款。</t>
@@ -1845,7 +1738,6 @@
           <t>2025年7月减资后股权结构</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
         <v>370</v>
       </c>
@@ -1854,16 +1746,2208 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>130.576</v>
       </c>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>2025年 3月25日，深圳三协召开股东会，决定深圳三协注册资本由人民币400.00万元减少至人民币370.00万元，减资后的股东变更为三合融创、朱南保，并修改章程相应条款。</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>上一时点(万股)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>本次变化(万股)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>预期值(万股)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PDF值(万股)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>差额</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴流量3条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>字段类型+非空检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>股权存量37条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>字段类型+t0存在检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>300</v>
+      </c>
+      <c r="E4" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1148.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>300</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-848.5</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t1-&gt;t10</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>300</v>
+      </c>
+      <c r="E5" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1148.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>355</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-793.5</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t10-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>355</v>
+      </c>
+      <c r="E6" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1203.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>300</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-903.5</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>300</v>
+      </c>
+      <c r="E7" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1148.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>300</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-848.5</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>300</v>
+      </c>
+      <c r="E8" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1148.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>400</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-748.5</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>400</v>
+      </c>
+      <c r="E9" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1248.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>400</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-848.5</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>400</v>
+      </c>
+      <c r="E10" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1248.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>377.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-871</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>t6-&gt;t7</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>377.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1226</v>
+      </c>
+      <c r="G11" t="n">
+        <v>417.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-808.5</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>t7-&gt;t8</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>417.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1266</v>
+      </c>
+      <c r="G12" t="n">
+        <v>417.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-848.5</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>t8-&gt;t9</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>417.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1266</v>
+      </c>
+      <c r="G13" t="n">
+        <v>377.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-888.5</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>德智高新</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>153</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>153</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-153</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>153</v>
+      </c>
+      <c r="H15" t="n">
+        <v>153</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>陆宇君</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>87</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>87</v>
+      </c>
+      <c r="G16" t="n">
+        <v>87</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>60</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>60</v>
+      </c>
+      <c r="G17" t="n">
+        <v>60</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>t1-&gt;t10</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>三合融创</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="H18" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>t1-&gt;t10</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>153</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>153</v>
+      </c>
+      <c r="G19" t="n">
+        <v>130.576</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-22.424</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>t1-&gt;t10</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>陆宇君</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>87</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>87</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-87</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>t1-&gt;t10</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>60</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>60</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-60</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>t10-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>三合融创</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-224.424</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>t10-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>卢娇娇</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>75</v>
+      </c>
+      <c r="H23" t="n">
+        <v>75</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>t10-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>130.576</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>130.576</v>
+      </c>
+      <c r="G24" t="n">
+        <v>90</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-40.576</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>t10-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>陆宇君</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>105</v>
+      </c>
+      <c r="H25" t="n">
+        <v>105</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>t10-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>30</v>
+      </c>
+      <c r="H26" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>卢娇娇</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>75</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>75</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-75</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>90</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>90</v>
+      </c>
+      <c r="G28" t="n">
+        <v>75</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-15</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>王洪波</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>陆宇君</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>105</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>105</v>
+      </c>
+      <c r="G30" t="n">
+        <v>105</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>30</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>30</v>
+      </c>
+      <c r="G31" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>75</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>75</v>
+      </c>
+      <c r="G32" t="n">
+        <v>85</v>
+      </c>
+      <c r="H32" t="n">
+        <v>10</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>王洪波</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>55</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>陆宇君</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>105</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>105</v>
+      </c>
+      <c r="G34" t="n">
+        <v>140</v>
+      </c>
+      <c r="H34" t="n">
+        <v>35</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>85</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>85</v>
+      </c>
+      <c r="G36" t="n">
+        <v>225</v>
+      </c>
+      <c r="H36" t="n">
+        <v>140</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>王洪波</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="G37" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>陆宇君</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>140</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>140</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-140</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G39" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>三合融创</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>130</v>
+      </c>
+      <c r="H40" t="n">
+        <v>130</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>225</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>225</v>
+      </c>
+      <c r="G41" t="n">
+        <v>225</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>王洪波</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-152.5</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G43" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>t6-&gt;t7</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>三合融创</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>130</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>130</v>
+      </c>
+      <c r="G44" t="n">
+        <v>130</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>t6-&gt;t7</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>225</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>225</v>
+      </c>
+      <c r="G45" t="n">
+        <v>225</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>t6-&gt;t7</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G46" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>t6-&gt;t7</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>黄晓彬</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>40</v>
+      </c>
+      <c r="H47" t="n">
+        <v>40</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>t7-&gt;t8</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>三合融创</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>130</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>130</v>
+      </c>
+      <c r="G48" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="H48" t="n">
+        <v>94.42400000000001</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>t7-&gt;t8</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>225</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>225</v>
+      </c>
+      <c r="G49" t="n">
+        <v>130.576</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-94.42400000000001</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>t7-&gt;t8</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G50" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>t7-&gt;t8</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>黄晓彬</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>40</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>40</v>
+      </c>
+      <c r="G51" t="n">
+        <v>40</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>t8-&gt;t9</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>三合融创</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="G52" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>t8-&gt;t9</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>130.576</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>130.576</v>
+      </c>
+      <c r="G53" t="n">
+        <v>130.576</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>t8-&gt;t9</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G54" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>t8-&gt;t9</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>黄晓彬</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>40</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>40</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-40</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/week2_excel/920100_三协电机_三表抽取.xlsx
+++ b/outputs/week2_excel/920100_三协电机_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -621,7 +622,6 @@
           <t>2019年5月深圳三协设立时股权结构</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>300</v>
       </c>
@@ -630,11 +630,9 @@
           <t>德智高新</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>153</v>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>2019年 5月15日，德智高新、陆宇君、陈广武共同签署《深圳市三协电机有限公司公司章程》，设立深圳三协，注册资本为人民币 300.00万元。其中，德智高新持有 51%的股权，陆宇君持有 29%的股权，陈广武持有20%的股权。</t>
@@ -655,7 +653,6 @@
           <t>2019年5月深圳三协设立时股权结构</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>300</v>
       </c>
@@ -664,11 +661,9 @@
           <t>陆宇君</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>87</v>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>2019年 5月15日，德智高新、陆宇君、陈广武共同签署《深圳市三协电机有限公司公司章程》，设立深圳三协，注册资本为人民币 300.00万元。其中，德智高新持有 51%的股权，陆宇君持有 29%的股权，陈广武持有20%的股权。</t>
@@ -689,7 +684,6 @@
           <t>2019年5月深圳三协设立时股权结构</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>300</v>
       </c>
@@ -698,11 +692,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>60</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>2019年 5月15日，德智高新、陆宇君、陈广武共同签署《深圳市三协电机有限公司公司章程》，设立深圳三协，注册资本为人民币 300.00万元。其中，德智高新持有 51%的股权，陆宇君持有 29%的股权，陈广武持有20%的股权。</t>
@@ -723,7 +715,6 @@
           <t>2019年7月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>300</v>
       </c>
@@ -732,11 +723,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>153</v>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>2019年 7月18日，深圳三协召开股东会，作出决议，同意股东德智高新将其所持公司 51%的股权转让给朱南保。</t>
@@ -757,7 +746,6 @@
           <t>2019年7月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
         <v>300</v>
       </c>
@@ -766,11 +754,9 @@
           <t>陆宇君</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>87</v>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>2019年 7月18日，深圳三协召开股东会，作出决议，同意股东德智高新将其所持公司 51%的股权转让给朱南保。</t>
@@ -791,7 +777,6 @@
           <t>2019年7月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
         <v>300</v>
       </c>
@@ -800,11 +785,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>60</v>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>2019年 7月18日，深圳三协召开股东会，作出决议，同意股东德智高新将其所持公司 51%的股权转让给朱南保。</t>
@@ -825,7 +808,6 @@
           <t>2019年12月/2020年1月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
         <v>300</v>
       </c>
@@ -834,11 +816,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>90</v>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>2019年 12月 4日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21%的股权转让给卢娇娇；同意股东陈广武将其所持公司4%的股权转让给卢娇娇；同意股东陈广武将其所持公司6%的股权转让给陆宇君。</t>
@@ -859,7 +839,6 @@
           <t>2019年12月/2020年1月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
         <v>300</v>
       </c>
@@ -868,11 +847,9 @@
           <t>陆宇君</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>105</v>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>2019年 12月 4日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21%的股权转让给卢娇娇；同意股东陈广武将其所持公司4%的股权转让给卢娇娇；同意股东陈广武将其所持公司6%的股权转让给陆宇君。</t>
@@ -893,7 +870,6 @@
           <t>2019年12月/2020年1月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
         <v>300</v>
       </c>
@@ -902,11 +878,9 @@
           <t>卢娇娇</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>75</v>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>2019年 12月 4日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21%的股权转让给卢娇娇；同意股东陈广武将其所持公司4%的股权转让给卢娇娇；同意股东陈广武将其所持公司6%的股权转让给陆宇君。</t>
@@ -927,7 +901,6 @@
           <t>2019年12月/2020年1月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
         <v>300</v>
       </c>
@@ -936,11 +909,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>30</v>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>2019年 12月 4日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21%的股权转让给卢娇娇；同意股东陈广武将其所持公司4%的股权转让给卢娇娇；同意股东陈广武将其所持公司6%的股权转让给陆宇君。</t>
@@ -961,7 +932,6 @@
           <t>2021年5月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
         <v>300</v>
       </c>
@@ -970,11 +940,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>75</v>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意股东卢娇娇将其所持公司 25%的股权转让给王洪波；同意股东朱南保将其所占公司5%的股权转让给王洪波；同意股东陈广武将其所占公司2.5%的股权转让给王洪波。</t>
@@ -995,7 +963,6 @@
           <t>2021年5月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
         <v>300</v>
       </c>
@@ -1004,11 +971,9 @@
           <t>陆宇君</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>105</v>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意股东卢娇娇将其所持公司 25%的股权转让给王洪波；同意股东朱南保将其所占公司5%的股权转让给王洪波；同意股东陈广武将其所占公司2.5%的股权转让给王洪波。</t>
@@ -1029,7 +994,6 @@
           <t>2021年5月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
         <v>300</v>
       </c>
@@ -1038,11 +1002,9 @@
           <t>王洪波</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>97.5</v>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意股东卢娇娇将其所持公司 25%的股权转让给王洪波；同意股东朱南保将其所占公司5%的股权转让给王洪波；同意股东陈广武将其所占公司2.5%的股权转让给王洪波。</t>
@@ -1063,7 +1025,6 @@
           <t>2021年5月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
         <v>300</v>
       </c>
@@ -1072,11 +1033,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>22.5</v>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意股东卢娇娇将其所持公司 25%的股权转让给王洪波；同意股东朱南保将其所占公司5%的股权转让给王洪波；同意股东陈广武将其所占公司2.5%的股权转让给王洪波。</t>
@@ -1097,7 +1056,6 @@
           <t>2021年5月增资后股权结构</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
         <v>400</v>
       </c>
@@ -1106,11 +1064,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>85</v>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意增加注册资本 100万元，即由原来 300 万元增加至400万元，由原股东同比例增资。其中，股东朱南保增加出资10 万元，股东陆宇君增加出资35万元，股东王洪波增加出资 55 万元。</t>
@@ -1131,7 +1087,6 @@
           <t>2021年5月增资后股权结构</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
         <v>400</v>
       </c>
@@ -1140,11 +1095,9 @@
           <t>陆宇君</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>140</v>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意增加注册资本 100万元，即由原来 300 万元增加至400万元，由原股东同比例增资。其中，股东朱南保增加出资10 万元，股东陆宇君增加出资35万元，股东王洪波增加出资 55 万元。</t>
@@ -1165,7 +1118,6 @@
           <t>2021年5月增资后股权结构</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
         <v>400</v>
       </c>
@@ -1174,11 +1126,9 @@
           <t>王洪波</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>152.5</v>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意增加注册资本 100万元，即由原来 300 万元增加至400万元，由原股东同比例增资。其中，股东朱南保增加出资10 万元，股东陆宇君增加出资35万元，股东王洪波增加出资 55 万元。</t>
@@ -1199,7 +1149,6 @@
           <t>2021年5月增资后股权结构</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
         <v>400</v>
       </c>
@@ -1208,11 +1157,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>22.5</v>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意增加注册资本 100万元，即由原来 300 万元增加至400万元，由原股东同比例增资。其中，股东朱南保增加出资10 万元，股东陆宇君增加出资35万元，股东王洪波增加出资 55 万元。</t>
@@ -1233,7 +1180,6 @@
           <t>2022年10月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
         <v>400</v>
       </c>
@@ -1242,11 +1188,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>225</v>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>2022年 10月 19日，深圳三协召开股东会，作出决议，同意股东陆宇君将其持有公司 35%的股权转让给朱南保。</t>
@@ -1267,7 +1211,6 @@
           <t>2022年10月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
         <v>400</v>
       </c>
@@ -1276,11 +1219,9 @@
           <t>王洪波</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>152.5</v>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>2022年 10月 19日，深圳三协召开股东会，作出决议，同意股东陆宇君将其持有公司 35%的股权转让给朱南保。</t>
@@ -1301,7 +1242,6 @@
           <t>2022年10月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
         <v>400</v>
       </c>
@@ -1310,11 +1250,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>22.5</v>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>2022年 10月 19日，深圳三协召开股东会，作出决议，同意股东陆宇君将其持有公司 35%的股权转让给朱南保。</t>
@@ -1335,7 +1273,6 @@
           <t>2022年11月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
         <v>400</v>
       </c>
@@ -1344,11 +1281,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>225</v>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>2022年 10月 26日，深圳三协召开股东会，作出决议，同意股东王洪波将其所持公司 32.5%的股权转让给发行人全资子公司三合融创。</t>
@@ -1369,7 +1304,6 @@
           <t>2022年11月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
         <v>400</v>
       </c>
@@ -1378,11 +1312,9 @@
           <t>三合融创</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>130</v>
       </c>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>2022年 10月 26日，深圳三协召开股东会，作出决议，同意股东王洪波将其所持公司 32.5%的股权转让给发行人全资子公司三合融创。</t>
@@ -1403,7 +1335,6 @@
           <t>2022年11月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
         <v>400</v>
       </c>
@@ -1412,11 +1343,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>22.5</v>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>2022年 10月 26日，深圳三协召开股东会，作出决议，同意股东王洪波将其所持公司 32.5%的股权转让给发行人全资子公司三合融创。</t>
@@ -1437,7 +1366,6 @@
           <t>2023年3月增资后股权结构</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
         <v>440</v>
       </c>
@@ -1446,11 +1374,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>225</v>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>2023年 3月30日，深圳三协召开股东会，全体股东一致同意将原注册资本 400万元变更为 440万元，由新股东黄晓彬认缴新增注册资本40万元。</t>
@@ -1471,7 +1397,6 @@
           <t>2023年3月增资后股权结构</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
         <v>440</v>
       </c>
@@ -1480,11 +1405,9 @@
           <t>三合融创</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>130</v>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>2023年 3月30日，深圳三协召开股东会，全体股东一致同意将原注册资本 400万元变更为 440万元，由新股东黄晓彬认缴新增注册资本40万元。</t>
@@ -1505,7 +1428,6 @@
           <t>2023年3月增资后股权结构</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
         <v>440</v>
       </c>
@@ -1514,11 +1436,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>22.5</v>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>2023年 3月30日，深圳三协召开股东会，全体股东一致同意将原注册资本 400万元变更为 440万元，由新股东黄晓彬认缴新增注册资本40万元。</t>
@@ -1539,7 +1459,6 @@
           <t>2023年3月增资后股权结构</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
         <v>440</v>
       </c>
@@ -1548,11 +1467,9 @@
           <t>黄晓彬</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>40</v>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>2023年 3月30日，深圳三协召开股东会，全体股东一致同意将原注册资本 400万元变更为 440万元，由新股东黄晓彬认缴新增注册资本40万元。</t>
@@ -1573,7 +1490,6 @@
           <t>2023年8月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
         <v>440</v>
       </c>
@@ -1582,11 +1498,9 @@
           <t>三合融创</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>224.424</v>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>2023年 8月21日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21.46%的股权转让给三合融创。</t>
@@ -1607,7 +1521,6 @@
           <t>2023年8月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
         <v>440</v>
       </c>
@@ -1616,11 +1529,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>130.576</v>
       </c>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>2023年 8月21日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21.46%的股权转让给三合融创。</t>
@@ -1641,7 +1552,6 @@
           <t>2023年8月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
         <v>440</v>
       </c>
@@ -1650,11 +1560,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>22.5</v>
       </c>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>2023年 8月21日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21.46%的股权转让给三合融创。</t>
@@ -1675,7 +1583,6 @@
           <t>2023年8月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
         <v>440</v>
       </c>
@@ -1684,11 +1591,9 @@
           <t>黄晓彬</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>40</v>
       </c>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>2023年 8月21日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21.46%的股权转让给三合融创。</t>
@@ -1709,7 +1614,6 @@
           <t>2024年6月减资后股权结构</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
         <v>400</v>
       </c>
@@ -1718,11 +1622,9 @@
           <t>三合融创</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>224.424</v>
       </c>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>2024年 3月1日，深圳三协召开股东会，决定深圳三协注册资本由人民币 440.00万元减少至人民币400.00万元，减资后的股东变更为三合融创、朱南保、陈广武，并修改章程相应条款。</t>
@@ -1743,7 +1645,6 @@
           <t>2024年6月减资后股权结构</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
         <v>400</v>
       </c>
@@ -1752,11 +1653,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>130.576</v>
       </c>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>2024年 3月1日，深圳三协召开股东会，决定深圳三协注册资本由人民币 440.00万元减少至人民币400.00万元，减资后的股东变更为三合融创、朱南保、陈广武，并修改章程相应条款。</t>
@@ -1777,7 +1676,6 @@
           <t>2024年6月减资后股权结构</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
         <v>400</v>
       </c>
@@ -1786,11 +1684,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>22.5</v>
       </c>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>2024年 3月1日，深圳三协召开股东会，决定深圳三协注册资本由人民币 440.00万元减少至人民币400.00万元，减资后的股东变更为三合融创、朱南保、陈广武，并修改章程相应条款。</t>
@@ -1811,7 +1707,6 @@
           <t>2025年7月减资后股权结构</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
         <v>370</v>
       </c>
@@ -1820,11 +1715,9 @@
           <t>三合融创</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>224.424</v>
       </c>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>2025年 3月25日，深圳三协召开股东会，决定深圳三协注册资本由人民币400.00万元减少至人民币370.00万元，减资后的股东变更为三合融创、朱南保，并修改章程相应条款。</t>
@@ -1845,7 +1738,6 @@
           <t>2025年7月减资后股权结构</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
         <v>370</v>
       </c>
@@ -1854,16 +1746,2144 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>130.576</v>
       </c>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>2025年 3月25日，深圳三协召开股东会，决定深圳三协注册资本由人民币400.00万元减少至人民币370.00万元，减资后的股东变更为三合融创、朱南保，并修改章程相应条款。</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>上一时点</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>本次变化</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>预期值</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PDF值</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>差额</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴3条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>字段类型+非空检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>存量37条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>t0存在+类型检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>300</v>
+      </c>
+      <c r="E4" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1148.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>300</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-848.5</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>德智高新</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>153</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>153</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-153</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>153</v>
+      </c>
+      <c r="H6" t="n">
+        <v>153</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>陆宇君</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>87</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>87</v>
+      </c>
+      <c r="G7" t="n">
+        <v>87</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>60</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>60</v>
+      </c>
+      <c r="G8" t="n">
+        <v>60</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>t1-&gt;t10</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>300</v>
+      </c>
+      <c r="E9" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1148.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>355</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-793.5</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>t1-&gt;t10</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>三合融创</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="H10" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>t1-&gt;t10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>153</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>153</v>
+      </c>
+      <c r="G11" t="n">
+        <v>130.576</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-22.424</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>t1-&gt;t10</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>陆宇君</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>87</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>87</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-87</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>t1-&gt;t10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>60</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>60</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-60</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>t10-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>355</v>
+      </c>
+      <c r="E14" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1203.5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>300</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-903.5</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>t10-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>三合融创</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-224.424</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>t10-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>卢娇娇</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>75</v>
+      </c>
+      <c r="H16" t="n">
+        <v>75</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>t10-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>130.576</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>130.576</v>
+      </c>
+      <c r="G17" t="n">
+        <v>90</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-40.576</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>t10-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>陆宇君</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>105</v>
+      </c>
+      <c r="H18" t="n">
+        <v>105</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>t10-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>30</v>
+      </c>
+      <c r="H19" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>300</v>
+      </c>
+      <c r="E20" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1148.5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>300</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-848.5</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>卢娇娇</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>75</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>75</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-75</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>90</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>90</v>
+      </c>
+      <c r="G22" t="n">
+        <v>75</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-15</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>王洪波</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>陆宇君</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>105</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>105</v>
+      </c>
+      <c r="G24" t="n">
+        <v>105</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>30</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>30</v>
+      </c>
+      <c r="G25" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>300</v>
+      </c>
+      <c r="E26" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1148.5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>400</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-748.5</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>75</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>75</v>
+      </c>
+      <c r="G27" t="n">
+        <v>85</v>
+      </c>
+      <c r="H27" t="n">
+        <v>10</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>王洪波</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>55</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>陆宇君</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>105</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>105</v>
+      </c>
+      <c r="G29" t="n">
+        <v>140</v>
+      </c>
+      <c r="H29" t="n">
+        <v>35</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>400</v>
+      </c>
+      <c r="E31" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1248.5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>400</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-848.5</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>85</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>85</v>
+      </c>
+      <c r="G32" t="n">
+        <v>225</v>
+      </c>
+      <c r="H32" t="n">
+        <v>140</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>王洪波</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>陆宇君</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>140</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>140</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-140</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>400</v>
+      </c>
+      <c r="E36" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1248.5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>377.5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-871</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>三合融创</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>130</v>
+      </c>
+      <c r="H37" t="n">
+        <v>130</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>225</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>225</v>
+      </c>
+      <c r="G38" t="n">
+        <v>225</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>王洪波</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-152.5</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G40" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>t6-&gt;t7</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>377.5</v>
+      </c>
+      <c r="E41" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1226</v>
+      </c>
+      <c r="G41" t="n">
+        <v>417.5</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-808.5</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>t6-&gt;t7</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>三合融创</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>130</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>130</v>
+      </c>
+      <c r="G42" t="n">
+        <v>130</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>t6-&gt;t7</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>225</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>225</v>
+      </c>
+      <c r="G43" t="n">
+        <v>225</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>t6-&gt;t7</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G44" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>t6-&gt;t7</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>黄晓彬</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>40</v>
+      </c>
+      <c r="H45" t="n">
+        <v>40</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>t7-&gt;t8</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>417.5</v>
+      </c>
+      <c r="E46" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1266</v>
+      </c>
+      <c r="G46" t="n">
+        <v>417.5</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-848.5</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>t7-&gt;t8</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>三合融创</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>130</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>130</v>
+      </c>
+      <c r="G47" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="H47" t="n">
+        <v>94.42400000000001</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>t7-&gt;t8</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>225</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>225</v>
+      </c>
+      <c r="G48" t="n">
+        <v>130.576</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-94.42400000000001</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>t7-&gt;t8</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G49" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>t7-&gt;t8</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>黄晓彬</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>40</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>40</v>
+      </c>
+      <c r="G50" t="n">
+        <v>40</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>t8-&gt;t9</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>417.5</v>
+      </c>
+      <c r="E51" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1266</v>
+      </c>
+      <c r="G51" t="n">
+        <v>377.5</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-888.5</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>t8-&gt;t9</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>三合融创</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="G52" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>t8-&gt;t9</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>130.576</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>130.576</v>
+      </c>
+      <c r="G53" t="n">
+        <v>130.576</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>t8-&gt;t9</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G54" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>t8-&gt;t9</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>黄晓彬</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>40</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>40</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-40</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/week2_excel/920100_三协电机_三表抽取.xlsx
+++ b/outputs/week2_excel/920100_三协电机_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -621,7 +622,6 @@
           <t>2019年5月深圳三协设立时股权结构</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>300</v>
       </c>
@@ -630,11 +630,9 @@
           <t>德智高新</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>153</v>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>2019年 5月15日，德智高新、陆宇君、陈广武共同签署《深圳市三协电机有限公司公司章程》，设立深圳三协，注册资本为人民币 300.00万元。其中，德智高新持有 51%的股权，陆宇君持有 29%的股权，陈广武持有20%的股权。</t>
@@ -655,7 +653,6 @@
           <t>2019年5月深圳三协设立时股权结构</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>300</v>
       </c>
@@ -664,11 +661,9 @@
           <t>陆宇君</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>87</v>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>2019年 5月15日，德智高新、陆宇君、陈广武共同签署《深圳市三协电机有限公司公司章程》，设立深圳三协，注册资本为人民币 300.00万元。其中，德智高新持有 51%的股权，陆宇君持有 29%的股权，陈广武持有20%的股权。</t>
@@ -689,7 +684,6 @@
           <t>2019年5月深圳三协设立时股权结构</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>300</v>
       </c>
@@ -698,11 +692,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>60</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>2019年 5月15日，德智高新、陆宇君、陈广武共同签署《深圳市三协电机有限公司公司章程》，设立深圳三协，注册资本为人民币 300.00万元。其中，德智高新持有 51%的股权，陆宇君持有 29%的股权，陈广武持有20%的股权。</t>
@@ -723,7 +715,6 @@
           <t>2019年7月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>300</v>
       </c>
@@ -732,11 +723,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>153</v>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>2019年 7月18日，深圳三协召开股东会，作出决议，同意股东德智高新将其所持公司 51%的股权转让给朱南保。</t>
@@ -757,7 +746,6 @@
           <t>2019年7月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
         <v>300</v>
       </c>
@@ -766,11 +754,9 @@
           <t>陆宇君</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>87</v>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>2019年 7月18日，深圳三协召开股东会，作出决议，同意股东德智高新将其所持公司 51%的股权转让给朱南保。</t>
@@ -791,7 +777,6 @@
           <t>2019年7月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
         <v>300</v>
       </c>
@@ -800,11 +785,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>60</v>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>2019年 7月18日，深圳三协召开股东会，作出决议，同意股东德智高新将其所持公司 51%的股权转让给朱南保。</t>
@@ -825,7 +808,6 @@
           <t>2019年12月/2020年1月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
         <v>300</v>
       </c>
@@ -834,11 +816,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>90</v>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>2019年 12月 4日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21%的股权转让给卢娇娇；同意股东陈广武将其所持公司4%的股权转让给卢娇娇；同意股东陈广武将其所持公司6%的股权转让给陆宇君。</t>
@@ -859,7 +839,6 @@
           <t>2019年12月/2020年1月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
         <v>300</v>
       </c>
@@ -868,11 +847,9 @@
           <t>陆宇君</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>105</v>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>2019年 12月 4日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21%的股权转让给卢娇娇；同意股东陈广武将其所持公司4%的股权转让给卢娇娇；同意股东陈广武将其所持公司6%的股权转让给陆宇君。</t>
@@ -893,7 +870,6 @@
           <t>2019年12月/2020年1月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
         <v>300</v>
       </c>
@@ -902,11 +878,9 @@
           <t>卢娇娇</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>75</v>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>2019年 12月 4日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21%的股权转让给卢娇娇；同意股东陈广武将其所持公司4%的股权转让给卢娇娇；同意股东陈广武将其所持公司6%的股权转让给陆宇君。</t>
@@ -927,7 +901,6 @@
           <t>2019年12月/2020年1月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
         <v>300</v>
       </c>
@@ -936,11 +909,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>30</v>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>2019年 12月 4日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21%的股权转让给卢娇娇；同意股东陈广武将其所持公司4%的股权转让给卢娇娇；同意股东陈广武将其所持公司6%的股权转让给陆宇君。</t>
@@ -961,7 +932,6 @@
           <t>2021年5月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
         <v>300</v>
       </c>
@@ -970,11 +940,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>75</v>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意股东卢娇娇将其所持公司 25%的股权转让给王洪波；同意股东朱南保将其所占公司5%的股权转让给王洪波；同意股东陈广武将其所占公司2.5%的股权转让给王洪波。</t>
@@ -995,7 +963,6 @@
           <t>2021年5月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
         <v>300</v>
       </c>
@@ -1004,11 +971,9 @@
           <t>陆宇君</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>105</v>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意股东卢娇娇将其所持公司 25%的股权转让给王洪波；同意股东朱南保将其所占公司5%的股权转让给王洪波；同意股东陈广武将其所占公司2.5%的股权转让给王洪波。</t>
@@ -1029,7 +994,6 @@
           <t>2021年5月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
         <v>300</v>
       </c>
@@ -1038,11 +1002,9 @@
           <t>王洪波</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>97.5</v>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意股东卢娇娇将其所持公司 25%的股权转让给王洪波；同意股东朱南保将其所占公司5%的股权转让给王洪波；同意股东陈广武将其所占公司2.5%的股权转让给王洪波。</t>
@@ -1063,7 +1025,6 @@
           <t>2021年5月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
         <v>300</v>
       </c>
@@ -1072,11 +1033,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>22.5</v>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意股东卢娇娇将其所持公司 25%的股权转让给王洪波；同意股东朱南保将其所占公司5%的股权转让给王洪波；同意股东陈广武将其所占公司2.5%的股权转让给王洪波。</t>
@@ -1097,7 +1056,6 @@
           <t>2021年5月增资后股权结构</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
         <v>400</v>
       </c>
@@ -1106,11 +1064,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>85</v>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意增加注册资本 100万元，即由原来 300 万元增加至400万元，由原股东同比例增资。其中，股东朱南保增加出资10 万元，股东陆宇君增加出资35万元，股东王洪波增加出资 55 万元。</t>
@@ -1131,7 +1087,6 @@
           <t>2021年5月增资后股权结构</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
         <v>400</v>
       </c>
@@ -1140,11 +1095,9 @@
           <t>陆宇君</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>140</v>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意增加注册资本 100万元，即由原来 300 万元增加至400万元，由原股东同比例增资。其中，股东朱南保增加出资10 万元，股东陆宇君增加出资35万元，股东王洪波增加出资 55 万元。</t>
@@ -1165,7 +1118,6 @@
           <t>2021年5月增资后股权结构</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
         <v>400</v>
       </c>
@@ -1174,11 +1126,9 @@
           <t>王洪波</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>152.5</v>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意增加注册资本 100万元，即由原来 300 万元增加至400万元，由原股东同比例增资。其中，股东朱南保增加出资10 万元，股东陆宇君增加出资35万元，股东王洪波增加出资 55 万元。</t>
@@ -1199,7 +1149,6 @@
           <t>2021年5月增资后股权结构</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
         <v>400</v>
       </c>
@@ -1208,11 +1157,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>22.5</v>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意增加注册资本 100万元，即由原来 300 万元增加至400万元，由原股东同比例增资。其中，股东朱南保增加出资10 万元，股东陆宇君增加出资35万元，股东王洪波增加出资 55 万元。</t>
@@ -1233,7 +1180,6 @@
           <t>2022年10月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
         <v>400</v>
       </c>
@@ -1242,11 +1188,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>225</v>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>2022年 10月 19日，深圳三协召开股东会，作出决议，同意股东陆宇君将其持有公司 35%的股权转让给朱南保。</t>
@@ -1267,7 +1211,6 @@
           <t>2022年10月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
         <v>400</v>
       </c>
@@ -1276,11 +1219,9 @@
           <t>王洪波</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>152.5</v>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>2022年 10月 19日，深圳三协召开股东会，作出决议，同意股东陆宇君将其持有公司 35%的股权转让给朱南保。</t>
@@ -1301,7 +1242,6 @@
           <t>2022年10月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
         <v>400</v>
       </c>
@@ -1310,11 +1250,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>22.5</v>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>2022年 10月 19日，深圳三协召开股东会，作出决议，同意股东陆宇君将其持有公司 35%的股权转让给朱南保。</t>
@@ -1335,7 +1273,6 @@
           <t>2022年11月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
         <v>400</v>
       </c>
@@ -1344,11 +1281,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>225</v>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>2022年 10月 26日，深圳三协召开股东会，作出决议，同意股东王洪波将其所持公司 32.5%的股权转让给发行人全资子公司三合融创。</t>
@@ -1369,7 +1304,6 @@
           <t>2022年11月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
         <v>400</v>
       </c>
@@ -1378,11 +1312,9 @@
           <t>三合融创</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>130</v>
       </c>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>2022年 10月 26日，深圳三协召开股东会，作出决议，同意股东王洪波将其所持公司 32.5%的股权转让给发行人全资子公司三合融创。</t>
@@ -1403,7 +1335,6 @@
           <t>2022年11月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
         <v>400</v>
       </c>
@@ -1412,11 +1343,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>22.5</v>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>2022年 10月 26日，深圳三协召开股东会，作出决议，同意股东王洪波将其所持公司 32.5%的股权转让给发行人全资子公司三合融创。</t>
@@ -1437,7 +1366,6 @@
           <t>2023年3月增资后股权结构</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
         <v>440</v>
       </c>
@@ -1446,11 +1374,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>225</v>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>2023年 3月30日，深圳三协召开股东会，全体股东一致同意将原注册资本 400万元变更为 440万元，由新股东黄晓彬认缴新增注册资本40万元。</t>
@@ -1471,7 +1397,6 @@
           <t>2023年3月增资后股权结构</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
         <v>440</v>
       </c>
@@ -1480,11 +1405,9 @@
           <t>三合融创</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>130</v>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>2023年 3月30日，深圳三协召开股东会，全体股东一致同意将原注册资本 400万元变更为 440万元，由新股东黄晓彬认缴新增注册资本40万元。</t>
@@ -1505,7 +1428,6 @@
           <t>2023年3月增资后股权结构</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
         <v>440</v>
       </c>
@@ -1514,11 +1436,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>22.5</v>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>2023年 3月30日，深圳三协召开股东会，全体股东一致同意将原注册资本 400万元变更为 440万元，由新股东黄晓彬认缴新增注册资本40万元。</t>
@@ -1539,7 +1459,6 @@
           <t>2023年3月增资后股权结构</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
         <v>440</v>
       </c>
@@ -1548,11 +1467,9 @@
           <t>黄晓彬</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>40</v>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>2023年 3月30日，深圳三协召开股东会，全体股东一致同意将原注册资本 400万元变更为 440万元，由新股东黄晓彬认缴新增注册资本40万元。</t>
@@ -1573,7 +1490,6 @@
           <t>2023年8月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
         <v>440</v>
       </c>
@@ -1582,11 +1498,9 @@
           <t>三合融创</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>224.424</v>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>2023年 8月21日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21.46%的股权转让给三合融创。</t>
@@ -1607,7 +1521,6 @@
           <t>2023年8月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
         <v>440</v>
       </c>
@@ -1616,11 +1529,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>130.576</v>
       </c>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>2023年 8月21日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21.46%的股权转让给三合融创。</t>
@@ -1641,7 +1552,6 @@
           <t>2023年8月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
         <v>440</v>
       </c>
@@ -1650,11 +1560,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>22.5</v>
       </c>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>2023年 8月21日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21.46%的股权转让给三合融创。</t>
@@ -1675,7 +1583,6 @@
           <t>2023年8月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
         <v>440</v>
       </c>
@@ -1684,11 +1591,9 @@
           <t>黄晓彬</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>40</v>
       </c>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>2023年 8月21日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21.46%的股权转让给三合融创。</t>
@@ -1709,7 +1614,6 @@
           <t>2024年6月减资后股权结构</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
         <v>400</v>
       </c>
@@ -1718,11 +1622,9 @@
           <t>三合融创</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>224.424</v>
       </c>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>2024年 3月1日，深圳三协召开股东会，决定深圳三协注册资本由人民币 440.00万元减少至人民币400.00万元，减资后的股东变更为三合融创、朱南保、陈广武，并修改章程相应条款。</t>
@@ -1743,7 +1645,6 @@
           <t>2024年6月减资后股权结构</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
         <v>400</v>
       </c>
@@ -1752,11 +1653,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>130.576</v>
       </c>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>2024年 3月1日，深圳三协召开股东会，决定深圳三协注册资本由人民币 440.00万元减少至人民币400.00万元，减资后的股东变更为三合融创、朱南保、陈广武，并修改章程相应条款。</t>
@@ -1777,7 +1676,6 @@
           <t>2024年6月减资后股权结构</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
         <v>400</v>
       </c>
@@ -1786,11 +1684,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>22.5</v>
       </c>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>2024年 3月1日，深圳三协召开股东会，决定深圳三协注册资本由人民币 440.00万元减少至人民币400.00万元，减资后的股东变更为三合融创、朱南保、陈广武，并修改章程相应条款。</t>
@@ -1811,7 +1707,6 @@
           <t>2025年7月减资后股权结构</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
         <v>370</v>
       </c>
@@ -1820,11 +1715,9 @@
           <t>三合融创</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>224.424</v>
       </c>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>2025年 3月25日，深圳三协召开股东会，决定深圳三协注册资本由人民币400.00万元减少至人民币370.00万元，减资后的股东变更为三合融创、朱南保，并修改章程相应条款。</t>
@@ -1845,7 +1738,6 @@
           <t>2025年7月减资后股权结构</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
         <v>370</v>
       </c>
@@ -1854,15 +1746,515 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>130.576</v>
       </c>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>2025年 3月25日，深圳三协召开股东会，决定深圳三协注册资本由人民币400.00万元减少至人民币370.00万元，减资后的股东变更为三合融创、朱南保，并修改章程相应条款。</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>上一时点(万股)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>本次变化</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>预期值</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>PDF值</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>差额</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴3条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>字段类型+非空检查通过</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>存量37条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>t0存在+类型检查通过</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>300</v>
+      </c>
+      <c r="G4" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1148.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>300</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-848.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t1-&gt;t10</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>300</v>
+      </c>
+      <c r="G5" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1148.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>355</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-793.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t10-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>355</v>
+      </c>
+      <c r="G6" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1203.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>300</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-903.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>300</v>
+      </c>
+      <c r="G7" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1148.5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>300</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-848.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G8" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1148.5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>400</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-748.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>400</v>
+      </c>
+      <c r="G9" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1248.5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>400</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-848.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>400</v>
+      </c>
+      <c r="G10" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1248.5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>377.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-871</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>t6-&gt;t7</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>377.5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1226</v>
+      </c>
+      <c r="I11" t="n">
+        <v>417.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-808.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>t7-&gt;t8</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>417.5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1266</v>
+      </c>
+      <c r="I12" t="n">
+        <v>417.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-848.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>t8-&gt;t9</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>417.5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1266</v>
+      </c>
+      <c r="I13" t="n">
+        <v>377.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-888.5</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/week2_excel/920100_三协电机_三表抽取.xlsx
+++ b/outputs/week2_excel/920100_三协电机_三表抽取.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -622,6 +621,7 @@
           <t>2019年5月深圳三协设立时股权结构</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>300</v>
       </c>
@@ -630,9 +630,11 @@
           <t>德智高新</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>153</v>
       </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>2019年 5月15日，德智高新、陆宇君、陈广武共同签署《深圳市三协电机有限公司公司章程》，设立深圳三协，注册资本为人民币 300.00万元。其中，德智高新持有 51%的股权，陆宇君持有 29%的股权，陈广武持有20%的股权。</t>
@@ -653,6 +655,7 @@
           <t>2019年5月深圳三协设立时股权结构</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>300</v>
       </c>
@@ -661,9 +664,11 @@
           <t>陆宇君</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>87</v>
       </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>2019年 5月15日，德智高新、陆宇君、陈广武共同签署《深圳市三协电机有限公司公司章程》，设立深圳三协，注册资本为人民币 300.00万元。其中，德智高新持有 51%的股权，陆宇君持有 29%的股权，陈广武持有20%的股权。</t>
@@ -684,6 +689,7 @@
           <t>2019年5月深圳三协设立时股权结构</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>300</v>
       </c>
@@ -692,9 +698,11 @@
           <t>陈广武</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>60</v>
       </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>2019年 5月15日，德智高新、陆宇君、陈广武共同签署《深圳市三协电机有限公司公司章程》，设立深圳三协，注册资本为人民币 300.00万元。其中，德智高新持有 51%的股权，陆宇君持有 29%的股权，陈广武持有20%的股权。</t>
@@ -715,6 +723,7 @@
           <t>2019年7月股权转让后股权结构</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>300</v>
       </c>
@@ -723,9 +732,11 @@
           <t>朱南保</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>153</v>
       </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>2019年 7月18日，深圳三协召开股东会，作出决议，同意股东德智高新将其所持公司 51%的股权转让给朱南保。</t>
@@ -746,6 +757,7 @@
           <t>2019年7月股权转让后股权结构</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
         <v>300</v>
       </c>
@@ -754,9 +766,11 @@
           <t>陆宇君</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>87</v>
       </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>2019年 7月18日，深圳三协召开股东会，作出决议，同意股东德智高新将其所持公司 51%的股权转让给朱南保。</t>
@@ -777,6 +791,7 @@
           <t>2019年7月股权转让后股权结构</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
         <v>300</v>
       </c>
@@ -785,9 +800,11 @@
           <t>陈广武</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>60</v>
       </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>2019年 7月18日，深圳三协召开股东会，作出决议，同意股东德智高新将其所持公司 51%的股权转让给朱南保。</t>
@@ -808,6 +825,7 @@
           <t>2019年12月/2020年1月股权转让后股权结构</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
         <v>300</v>
       </c>
@@ -816,9 +834,11 @@
           <t>朱南保</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>90</v>
       </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>2019年 12月 4日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21%的股权转让给卢娇娇；同意股东陈广武将其所持公司4%的股权转让给卢娇娇；同意股东陈广武将其所持公司6%的股权转让给陆宇君。</t>
@@ -839,6 +859,7 @@
           <t>2019年12月/2020年1月股权转让后股权结构</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
         <v>300</v>
       </c>
@@ -847,9 +868,11 @@
           <t>陆宇君</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>105</v>
       </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>2019年 12月 4日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21%的股权转让给卢娇娇；同意股东陈广武将其所持公司4%的股权转让给卢娇娇；同意股东陈广武将其所持公司6%的股权转让给陆宇君。</t>
@@ -870,6 +893,7 @@
           <t>2019年12月/2020年1月股权转让后股权结构</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
         <v>300</v>
       </c>
@@ -878,9 +902,11 @@
           <t>卢娇娇</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>75</v>
       </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>2019年 12月 4日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21%的股权转让给卢娇娇；同意股东陈广武将其所持公司4%的股权转让给卢娇娇；同意股东陈广武将其所持公司6%的股权转让给陆宇君。</t>
@@ -901,6 +927,7 @@
           <t>2019年12月/2020年1月股权转让后股权结构</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
         <v>300</v>
       </c>
@@ -909,9 +936,11 @@
           <t>陈广武</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>30</v>
       </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>2019年 12月 4日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21%的股权转让给卢娇娇；同意股东陈广武将其所持公司4%的股权转让给卢娇娇；同意股东陈广武将其所持公司6%的股权转让给陆宇君。</t>
@@ -932,6 +961,7 @@
           <t>2021年5月股权转让后股权结构</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
         <v>300</v>
       </c>
@@ -940,9 +970,11 @@
           <t>朱南保</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>75</v>
       </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意股东卢娇娇将其所持公司 25%的股权转让给王洪波；同意股东朱南保将其所占公司5%的股权转让给王洪波；同意股东陈广武将其所占公司2.5%的股权转让给王洪波。</t>
@@ -963,6 +995,7 @@
           <t>2021年5月股权转让后股权结构</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
         <v>300</v>
       </c>
@@ -971,9 +1004,11 @@
           <t>陆宇君</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>105</v>
       </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意股东卢娇娇将其所持公司 25%的股权转让给王洪波；同意股东朱南保将其所占公司5%的股权转让给王洪波；同意股东陈广武将其所占公司2.5%的股权转让给王洪波。</t>
@@ -994,6 +1029,7 @@
           <t>2021年5月股权转让后股权结构</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
         <v>300</v>
       </c>
@@ -1002,9 +1038,11 @@
           <t>王洪波</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>97.5</v>
       </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意股东卢娇娇将其所持公司 25%的股权转让给王洪波；同意股东朱南保将其所占公司5%的股权转让给王洪波；同意股东陈广武将其所占公司2.5%的股权转让给王洪波。</t>
@@ -1025,6 +1063,7 @@
           <t>2021年5月股权转让后股权结构</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
         <v>300</v>
       </c>
@@ -1033,9 +1072,11 @@
           <t>陈广武</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>22.5</v>
       </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意股东卢娇娇将其所持公司 25%的股权转让给王洪波；同意股东朱南保将其所占公司5%的股权转让给王洪波；同意股东陈广武将其所占公司2.5%的股权转让给王洪波。</t>
@@ -1056,6 +1097,7 @@
           <t>2021年5月增资后股权结构</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
         <v>400</v>
       </c>
@@ -1064,9 +1106,11 @@
           <t>朱南保</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>85</v>
       </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意增加注册资本 100万元，即由原来 300 万元增加至400万元，由原股东同比例增资。其中，股东朱南保增加出资10 万元，股东陆宇君增加出资35万元，股东王洪波增加出资 55 万元。</t>
@@ -1087,6 +1131,7 @@
           <t>2021年5月增资后股权结构</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
         <v>400</v>
       </c>
@@ -1095,9 +1140,11 @@
           <t>陆宇君</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>140</v>
       </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意增加注册资本 100万元，即由原来 300 万元增加至400万元，由原股东同比例增资。其中，股东朱南保增加出资10 万元，股东陆宇君增加出资35万元，股东王洪波增加出资 55 万元。</t>
@@ -1118,6 +1165,7 @@
           <t>2021年5月增资后股权结构</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
         <v>400</v>
       </c>
@@ -1126,9 +1174,11 @@
           <t>王洪波</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>152.5</v>
       </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意增加注册资本 100万元，即由原来 300 万元增加至400万元，由原股东同比例增资。其中，股东朱南保增加出资10 万元，股东陆宇君增加出资35万元，股东王洪波增加出资 55 万元。</t>
@@ -1149,6 +1199,7 @@
           <t>2021年5月增资后股权结构</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
         <v>400</v>
       </c>
@@ -1157,9 +1208,11 @@
           <t>陈广武</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>22.5</v>
       </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意增加注册资本 100万元，即由原来 300 万元增加至400万元，由原股东同比例增资。其中，股东朱南保增加出资10 万元，股东陆宇君增加出资35万元，股东王洪波增加出资 55 万元。</t>
@@ -1180,6 +1233,7 @@
           <t>2022年10月股权转让后股权结构</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
         <v>400</v>
       </c>
@@ -1188,9 +1242,11 @@
           <t>朱南保</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>225</v>
       </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>2022年 10月 19日，深圳三协召开股东会，作出决议，同意股东陆宇君将其持有公司 35%的股权转让给朱南保。</t>
@@ -1211,6 +1267,7 @@
           <t>2022年10月股权转让后股权结构</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
         <v>400</v>
       </c>
@@ -1219,9 +1276,11 @@
           <t>王洪波</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>152.5</v>
       </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>2022年 10月 19日，深圳三协召开股东会，作出决议，同意股东陆宇君将其持有公司 35%的股权转让给朱南保。</t>
@@ -1242,6 +1301,7 @@
           <t>2022年10月股权转让后股权结构</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
         <v>400</v>
       </c>
@@ -1250,9 +1310,11 @@
           <t>陈广武</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>22.5</v>
       </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>2022年 10月 19日，深圳三协召开股东会，作出决议，同意股东陆宇君将其持有公司 35%的股权转让给朱南保。</t>
@@ -1273,6 +1335,7 @@
           <t>2022年11月股权转让后股权结构</t>
         </is>
       </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
         <v>400</v>
       </c>
@@ -1281,9 +1344,11 @@
           <t>朱南保</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>225</v>
       </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>2022年 10月 26日，深圳三协召开股东会，作出决议，同意股东王洪波将其所持公司 32.5%的股权转让给发行人全资子公司三合融创。</t>
@@ -1304,6 +1369,7 @@
           <t>2022年11月股权转让后股权结构</t>
         </is>
       </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
         <v>400</v>
       </c>
@@ -1312,9 +1378,11 @@
           <t>三合融创</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>130</v>
       </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>2022年 10月 26日，深圳三协召开股东会，作出决议，同意股东王洪波将其所持公司 32.5%的股权转让给发行人全资子公司三合融创。</t>
@@ -1335,6 +1403,7 @@
           <t>2022年11月股权转让后股权结构</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
         <v>400</v>
       </c>
@@ -1343,9 +1412,11 @@
           <t>陈广武</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>22.5</v>
       </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>2022年 10月 26日，深圳三协召开股东会，作出决议，同意股东王洪波将其所持公司 32.5%的股权转让给发行人全资子公司三合融创。</t>
@@ -1366,6 +1437,7 @@
           <t>2023年3月增资后股权结构</t>
         </is>
       </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
         <v>440</v>
       </c>
@@ -1374,9 +1446,11 @@
           <t>朱南保</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>225</v>
       </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>2023年 3月30日，深圳三协召开股东会，全体股东一致同意将原注册资本 400万元变更为 440万元，由新股东黄晓彬认缴新增注册资本40万元。</t>
@@ -1397,6 +1471,7 @@
           <t>2023年3月增资后股权结构</t>
         </is>
       </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
         <v>440</v>
       </c>
@@ -1405,9 +1480,11 @@
           <t>三合融创</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>130</v>
       </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>2023年 3月30日，深圳三协召开股东会，全体股东一致同意将原注册资本 400万元变更为 440万元，由新股东黄晓彬认缴新增注册资本40万元。</t>
@@ -1428,6 +1505,7 @@
           <t>2023年3月增资后股权结构</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
         <v>440</v>
       </c>
@@ -1436,9 +1514,11 @@
           <t>陈广武</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>22.5</v>
       </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>2023年 3月30日，深圳三协召开股东会，全体股东一致同意将原注册资本 400万元变更为 440万元，由新股东黄晓彬认缴新增注册资本40万元。</t>
@@ -1459,6 +1539,7 @@
           <t>2023年3月增资后股权结构</t>
         </is>
       </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
         <v>440</v>
       </c>
@@ -1467,9 +1548,11 @@
           <t>黄晓彬</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>40</v>
       </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>2023年 3月30日，深圳三协召开股东会，全体股东一致同意将原注册资本 400万元变更为 440万元，由新股东黄晓彬认缴新增注册资本40万元。</t>
@@ -1490,6 +1573,7 @@
           <t>2023年8月股权转让后股权结构</t>
         </is>
       </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
         <v>440</v>
       </c>
@@ -1498,9 +1582,11 @@
           <t>三合融创</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>224.424</v>
       </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>2023年 8月21日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21.46%的股权转让给三合融创。</t>
@@ -1521,6 +1607,7 @@
           <t>2023年8月股权转让后股权结构</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
         <v>440</v>
       </c>
@@ -1529,9 +1616,11 @@
           <t>朱南保</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>130.576</v>
       </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>2023年 8月21日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21.46%的股权转让给三合融创。</t>
@@ -1552,6 +1641,7 @@
           <t>2023年8月股权转让后股权结构</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
         <v>440</v>
       </c>
@@ -1560,9 +1650,11 @@
           <t>陈广武</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>22.5</v>
       </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>2023年 8月21日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21.46%的股权转让给三合融创。</t>
@@ -1583,6 +1675,7 @@
           <t>2023年8月股权转让后股权结构</t>
         </is>
       </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
         <v>440</v>
       </c>
@@ -1591,9 +1684,11 @@
           <t>黄晓彬</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>40</v>
       </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>2023年 8月21日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21.46%的股权转让给三合融创。</t>
@@ -1614,6 +1709,7 @@
           <t>2024年6月减资后股权结构</t>
         </is>
       </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
         <v>400</v>
       </c>
@@ -1622,9 +1718,11 @@
           <t>三合融创</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>224.424</v>
       </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>2024年 3月1日，深圳三协召开股东会，决定深圳三协注册资本由人民币 440.00万元减少至人民币400.00万元，减资后的股东变更为三合融创、朱南保、陈广武，并修改章程相应条款。</t>
@@ -1645,6 +1743,7 @@
           <t>2024年6月减资后股权结构</t>
         </is>
       </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
         <v>400</v>
       </c>
@@ -1653,9 +1752,11 @@
           <t>朱南保</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>130.576</v>
       </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>2024年 3月1日，深圳三协召开股东会，决定深圳三协注册资本由人民币 440.00万元减少至人民币400.00万元，减资后的股东变更为三合融创、朱南保、陈广武，并修改章程相应条款。</t>
@@ -1676,6 +1777,7 @@
           <t>2024年6月减资后股权结构</t>
         </is>
       </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
         <v>400</v>
       </c>
@@ -1684,9 +1786,11 @@
           <t>陈广武</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>22.5</v>
       </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>2024年 3月1日，深圳三协召开股东会，决定深圳三协注册资本由人民币 440.00万元减少至人民币400.00万元，减资后的股东变更为三合融创、朱南保、陈广武，并修改章程相应条款。</t>
@@ -1707,6 +1811,7 @@
           <t>2025年7月减资后股权结构</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
         <v>370</v>
       </c>
@@ -1715,9 +1820,11 @@
           <t>三合融创</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>224.424</v>
       </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>2025年 3月25日，深圳三协召开股东会，决定深圳三协注册资本由人民币400.00万元减少至人民币370.00万元，减资后的股东变更为三合融创、朱南保，并修改章程相应条款。</t>
@@ -1738,6 +1845,7 @@
           <t>2025年7月减资后股权结构</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
         <v>370</v>
       </c>
@@ -1746,515 +1854,15 @@
           <t>朱南保</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>130.576</v>
       </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>2025年 3月25日，深圳三协召开股东会，决定深圳三协注册资本由人民币400.00万元减少至人民币370.00万元，减资后的股东变更为三合融创、朱南保，并修改章程相应条款。</t>
         </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>检查类型</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>时点</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>股东</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>校验结果</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>上一时点(万股)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>本次变化</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>预期值</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>PDF值</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>差额</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>认缴3条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>字段类型+非空检查通过</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>存量37条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>t0存在+类型检查通过</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="n">
-        <v>300</v>
-      </c>
-      <c r="G4" t="n">
-        <v>848.5</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1148.5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>300</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-848.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>t1-&gt;t10</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
-        <v>300</v>
-      </c>
-      <c r="G5" t="n">
-        <v>848.5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1148.5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>355</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-793.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>t10-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="n">
-        <v>355</v>
-      </c>
-      <c r="G6" t="n">
-        <v>848.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1203.5</v>
-      </c>
-      <c r="I6" t="n">
-        <v>300</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-903.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="n">
-        <v>300</v>
-      </c>
-      <c r="G7" t="n">
-        <v>848.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1148.5</v>
-      </c>
-      <c r="I7" t="n">
-        <v>300</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-848.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G8" t="n">
-        <v>848.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1148.5</v>
-      </c>
-      <c r="I8" t="n">
-        <v>400</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-748.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>400</v>
-      </c>
-      <c r="G9" t="n">
-        <v>848.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1248.5</v>
-      </c>
-      <c r="I9" t="n">
-        <v>400</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-848.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="n">
-        <v>400</v>
-      </c>
-      <c r="G10" t="n">
-        <v>848.5</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1248.5</v>
-      </c>
-      <c r="I10" t="n">
-        <v>377.5</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-871</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>t6-&gt;t7</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="n">
-        <v>377.5</v>
-      </c>
-      <c r="G11" t="n">
-        <v>848.5</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1226</v>
-      </c>
-      <c r="I11" t="n">
-        <v>417.5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>-808.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>t7-&gt;t8</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="n">
-        <v>417.5</v>
-      </c>
-      <c r="G12" t="n">
-        <v>848.5</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1266</v>
-      </c>
-      <c r="I12" t="n">
-        <v>417.5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>-848.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>t8-&gt;t9</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="n">
-        <v>417.5</v>
-      </c>
-      <c r="G13" t="n">
-        <v>848.5</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1266</v>
-      </c>
-      <c r="I13" t="n">
-        <v>377.5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>-888.5</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/week2_excel/920100_三协电机_三表抽取.xlsx
+++ b/outputs/week2_excel/920100_三协电机_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -621,7 +622,6 @@
           <t>2019年5月深圳三协设立时股权结构</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>300</v>
       </c>
@@ -630,11 +630,9 @@
           <t>德智高新</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>153</v>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>2019年 5月15日，德智高新、陆宇君、陈广武共同签署《深圳市三协电机有限公司公司章程》，设立深圳三协，注册资本为人民币 300.00万元。其中，德智高新持有 51%的股权，陆宇君持有 29%的股权，陈广武持有20%的股权。</t>
@@ -655,7 +653,6 @@
           <t>2019年5月深圳三协设立时股权结构</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>300</v>
       </c>
@@ -664,11 +661,9 @@
           <t>陆宇君</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>87</v>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>2019年 5月15日，德智高新、陆宇君、陈广武共同签署《深圳市三协电机有限公司公司章程》，设立深圳三协，注册资本为人民币 300.00万元。其中，德智高新持有 51%的股权，陆宇君持有 29%的股权，陈广武持有20%的股权。</t>
@@ -689,7 +684,6 @@
           <t>2019年5月深圳三协设立时股权结构</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>300</v>
       </c>
@@ -698,11 +692,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>60</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>2019年 5月15日，德智高新、陆宇君、陈广武共同签署《深圳市三协电机有限公司公司章程》，设立深圳三协，注册资本为人民币 300.00万元。其中，德智高新持有 51%的股权，陆宇君持有 29%的股权，陈广武持有20%的股权。</t>
@@ -723,7 +715,6 @@
           <t>2019年7月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>300</v>
       </c>
@@ -732,11 +723,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>153</v>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>2019年 7月18日，深圳三协召开股东会，作出决议，同意股东德智高新将其所持公司 51%的股权转让给朱南保。</t>
@@ -757,7 +746,6 @@
           <t>2019年7月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
         <v>300</v>
       </c>
@@ -766,11 +754,9 @@
           <t>陆宇君</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>87</v>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>2019年 7月18日，深圳三协召开股东会，作出决议，同意股东德智高新将其所持公司 51%的股权转让给朱南保。</t>
@@ -791,7 +777,6 @@
           <t>2019年7月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
         <v>300</v>
       </c>
@@ -800,11 +785,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>60</v>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>2019年 7月18日，深圳三协召开股东会，作出决议，同意股东德智高新将其所持公司 51%的股权转让给朱南保。</t>
@@ -825,7 +808,6 @@
           <t>2019年12月/2020年1月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
         <v>300</v>
       </c>
@@ -834,11 +816,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>90</v>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>2019年 12月 4日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21%的股权转让给卢娇娇；同意股东陈广武将其所持公司4%的股权转让给卢娇娇；同意股东陈广武将其所持公司6%的股权转让给陆宇君。</t>
@@ -859,7 +839,6 @@
           <t>2019年12月/2020年1月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
         <v>300</v>
       </c>
@@ -868,11 +847,9 @@
           <t>陆宇君</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>105</v>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>2019年 12月 4日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21%的股权转让给卢娇娇；同意股东陈广武将其所持公司4%的股权转让给卢娇娇；同意股东陈广武将其所持公司6%的股权转让给陆宇君。</t>
@@ -893,7 +870,6 @@
           <t>2019年12月/2020年1月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
         <v>300</v>
       </c>
@@ -902,11 +878,9 @@
           <t>卢娇娇</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>75</v>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>2019年 12月 4日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21%的股权转让给卢娇娇；同意股东陈广武将其所持公司4%的股权转让给卢娇娇；同意股东陈广武将其所持公司6%的股权转让给陆宇君。</t>
@@ -927,7 +901,6 @@
           <t>2019年12月/2020年1月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
         <v>300</v>
       </c>
@@ -936,11 +909,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>30</v>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>2019年 12月 4日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21%的股权转让给卢娇娇；同意股东陈广武将其所持公司4%的股权转让给卢娇娇；同意股东陈广武将其所持公司6%的股权转让给陆宇君。</t>
@@ -961,7 +932,6 @@
           <t>2021年5月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
         <v>300</v>
       </c>
@@ -970,11 +940,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>75</v>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意股东卢娇娇将其所持公司 25%的股权转让给王洪波；同意股东朱南保将其所占公司5%的股权转让给王洪波；同意股东陈广武将其所占公司2.5%的股权转让给王洪波。</t>
@@ -995,7 +963,6 @@
           <t>2021年5月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
         <v>300</v>
       </c>
@@ -1004,11 +971,9 @@
           <t>陆宇君</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>105</v>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意股东卢娇娇将其所持公司 25%的股权转让给王洪波；同意股东朱南保将其所占公司5%的股权转让给王洪波；同意股东陈广武将其所占公司2.5%的股权转让给王洪波。</t>
@@ -1029,7 +994,6 @@
           <t>2021年5月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
         <v>300</v>
       </c>
@@ -1038,11 +1002,9 @@
           <t>王洪波</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>97.5</v>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意股东卢娇娇将其所持公司 25%的股权转让给王洪波；同意股东朱南保将其所占公司5%的股权转让给王洪波；同意股东陈广武将其所占公司2.5%的股权转让给王洪波。</t>
@@ -1063,7 +1025,6 @@
           <t>2021年5月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
         <v>300</v>
       </c>
@@ -1072,11 +1033,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>22.5</v>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意股东卢娇娇将其所持公司 25%的股权转让给王洪波；同意股东朱南保将其所占公司5%的股权转让给王洪波；同意股东陈广武将其所占公司2.5%的股权转让给王洪波。</t>
@@ -1097,7 +1056,6 @@
           <t>2021年5月增资后股权结构</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
         <v>400</v>
       </c>
@@ -1106,11 +1064,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>85</v>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意增加注册资本 100万元，即由原来 300 万元增加至400万元，由原股东同比例增资。其中，股东朱南保增加出资10 万元，股东陆宇君增加出资35万元，股东王洪波增加出资 55 万元。</t>
@@ -1131,7 +1087,6 @@
           <t>2021年5月增资后股权结构</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
         <v>400</v>
       </c>
@@ -1140,11 +1095,9 @@
           <t>陆宇君</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>140</v>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意增加注册资本 100万元，即由原来 300 万元增加至400万元，由原股东同比例增资。其中，股东朱南保增加出资10 万元，股东陆宇君增加出资35万元，股东王洪波增加出资 55 万元。</t>
@@ -1165,7 +1118,6 @@
           <t>2021年5月增资后股权结构</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
         <v>400</v>
       </c>
@@ -1174,11 +1126,9 @@
           <t>王洪波</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>152.5</v>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意增加注册资本 100万元，即由原来 300 万元增加至400万元，由原股东同比例增资。其中，股东朱南保增加出资10 万元，股东陆宇君增加出资35万元，股东王洪波增加出资 55 万元。</t>
@@ -1199,7 +1149,6 @@
           <t>2021年5月增资后股权结构</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
         <v>400</v>
       </c>
@@ -1208,11 +1157,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>22.5</v>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意增加注册资本 100万元，即由原来 300 万元增加至400万元，由原股东同比例增资。其中，股东朱南保增加出资10 万元，股东陆宇君增加出资35万元，股东王洪波增加出资 55 万元。</t>
@@ -1233,7 +1180,6 @@
           <t>2022年10月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
         <v>400</v>
       </c>
@@ -1242,11 +1188,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>225</v>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>2022年 10月 19日，深圳三协召开股东会，作出决议，同意股东陆宇君将其持有公司 35%的股权转让给朱南保。</t>
@@ -1267,7 +1211,6 @@
           <t>2022年10月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
         <v>400</v>
       </c>
@@ -1276,11 +1219,9 @@
           <t>王洪波</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>152.5</v>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>2022年 10月 19日，深圳三协召开股东会，作出决议，同意股东陆宇君将其持有公司 35%的股权转让给朱南保。</t>
@@ -1301,7 +1242,6 @@
           <t>2022年10月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
         <v>400</v>
       </c>
@@ -1310,11 +1250,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>22.5</v>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>2022年 10月 19日，深圳三协召开股东会，作出决议，同意股东陆宇君将其持有公司 35%的股权转让给朱南保。</t>
@@ -1335,7 +1273,6 @@
           <t>2022年11月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
         <v>400</v>
       </c>
@@ -1344,11 +1281,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>225</v>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>2022年 10月 26日，深圳三协召开股东会，作出决议，同意股东王洪波将其所持公司 32.5%的股权转让给发行人全资子公司三合融创。</t>
@@ -1369,7 +1304,6 @@
           <t>2022年11月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
         <v>400</v>
       </c>
@@ -1378,11 +1312,9 @@
           <t>三合融创</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>130</v>
       </c>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>2022年 10月 26日，深圳三协召开股东会，作出决议，同意股东王洪波将其所持公司 32.5%的股权转让给发行人全资子公司三合融创。</t>
@@ -1403,7 +1335,6 @@
           <t>2022年11月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
         <v>400</v>
       </c>
@@ -1412,11 +1343,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>22.5</v>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>2022年 10月 26日，深圳三协召开股东会，作出决议，同意股东王洪波将其所持公司 32.5%的股权转让给发行人全资子公司三合融创。</t>
@@ -1437,7 +1366,6 @@
           <t>2023年3月增资后股权结构</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
         <v>440</v>
       </c>
@@ -1446,11 +1374,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>225</v>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>2023年 3月30日，深圳三协召开股东会，全体股东一致同意将原注册资本 400万元变更为 440万元，由新股东黄晓彬认缴新增注册资本40万元。</t>
@@ -1471,7 +1397,6 @@
           <t>2023年3月增资后股权结构</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
         <v>440</v>
       </c>
@@ -1480,11 +1405,9 @@
           <t>三合融创</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>130</v>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>2023年 3月30日，深圳三协召开股东会，全体股东一致同意将原注册资本 400万元变更为 440万元，由新股东黄晓彬认缴新增注册资本40万元。</t>
@@ -1505,7 +1428,6 @@
           <t>2023年3月增资后股权结构</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
         <v>440</v>
       </c>
@@ -1514,11 +1436,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>22.5</v>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>2023年 3月30日，深圳三协召开股东会，全体股东一致同意将原注册资本 400万元变更为 440万元，由新股东黄晓彬认缴新增注册资本40万元。</t>
@@ -1539,7 +1459,6 @@
           <t>2023年3月增资后股权结构</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
         <v>440</v>
       </c>
@@ -1548,11 +1467,9 @@
           <t>黄晓彬</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>40</v>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>2023年 3月30日，深圳三协召开股东会，全体股东一致同意将原注册资本 400万元变更为 440万元，由新股东黄晓彬认缴新增注册资本40万元。</t>
@@ -1573,7 +1490,6 @@
           <t>2023年8月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
         <v>440</v>
       </c>
@@ -1582,11 +1498,9 @@
           <t>三合融创</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>224.424</v>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>2023年 8月21日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21.46%的股权转让给三合融创。</t>
@@ -1607,7 +1521,6 @@
           <t>2023年8月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
         <v>440</v>
       </c>
@@ -1616,11 +1529,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>130.576</v>
       </c>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>2023年 8月21日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21.46%的股权转让给三合融创。</t>
@@ -1641,7 +1552,6 @@
           <t>2023年8月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
         <v>440</v>
       </c>
@@ -1650,11 +1560,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>22.5</v>
       </c>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>2023年 8月21日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21.46%的股权转让给三合融创。</t>
@@ -1675,7 +1583,6 @@
           <t>2023年8月股权转让后股权结构</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
         <v>440</v>
       </c>
@@ -1684,11 +1591,9 @@
           <t>黄晓彬</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>40</v>
       </c>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>2023年 8月21日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21.46%的股权转让给三合融创。</t>
@@ -1709,7 +1614,6 @@
           <t>2024年6月减资后股权结构</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
         <v>400</v>
       </c>
@@ -1718,11 +1622,9 @@
           <t>三合融创</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>224.424</v>
       </c>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>2024年 3月1日，深圳三协召开股东会，决定深圳三协注册资本由人民币 440.00万元减少至人民币400.00万元，减资后的股东变更为三合融创、朱南保、陈广武，并修改章程相应条款。</t>
@@ -1743,7 +1645,6 @@
           <t>2024年6月减资后股权结构</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
         <v>400</v>
       </c>
@@ -1752,11 +1653,9 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>130.576</v>
       </c>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>2024年 3月1日，深圳三协召开股东会，决定深圳三协注册资本由人民币 440.00万元减少至人民币400.00万元，减资后的股东变更为三合融创、朱南保、陈广武，并修改章程相应条款。</t>
@@ -1777,7 +1676,6 @@
           <t>2024年6月减资后股权结构</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
         <v>400</v>
       </c>
@@ -1786,11 +1684,9 @@
           <t>陈广武</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>22.5</v>
       </c>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>2024年 3月1日，深圳三协召开股东会，决定深圳三协注册资本由人民币 440.00万元减少至人民币400.00万元，减资后的股东变更为三合融创、朱南保、陈广武，并修改章程相应条款。</t>
@@ -1811,7 +1707,6 @@
           <t>2025年7月减资后股权结构</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
         <v>370</v>
       </c>
@@ -1820,11 +1715,9 @@
           <t>三合融创</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>224.424</v>
       </c>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>2025年 3月25日，深圳三协召开股东会，决定深圳三协注册资本由人民币400.00万元减少至人民币370.00万元，减资后的股东变更为三合融创、朱南保，并修改章程相应条款。</t>
@@ -1845,7 +1738,6 @@
           <t>2025年7月减资后股权结构</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
         <v>370</v>
       </c>
@@ -1854,14 +1746,122 @@
           <t>朱南保</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>130.576</v>
       </c>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>2025年 3月25日，深圳三协召开股东会，决定深圳三协注册资本由人民币400.00万元减少至人民币370.00万元，减资后的股东变更为三合融创、朱南保，并修改章程相应条款。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴3条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>字段完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>存量37条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>t0存在</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>转让10条</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>已合并</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/920100_三协电机_三表抽取.xlsx
+++ b/outputs/week2_excel/920100_三协电机_三表抽取.xlsx
@@ -1766,7 +1766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1777,20 +1777,45 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>时点</t>
+          <t>PDF页码</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>股东</t>
+          <t>股东/认购方</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>上一时点(万股)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>本次变化(万股)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>预期值(万股)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PDF值(万股)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>差额(万股)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>校验结果</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -1805,17 +1830,22 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>认缴3条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+          <t>认缴流量</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>字段完整</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>3条,字段完整</t>
         </is>
       </c>
     </row>
@@ -1828,40 +1858,2306 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>存量37条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+          <t>股权存量</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>t0存在</t>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>37条,t0存在</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>schema</t>
+          <t>cross_check_total</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>转让10条</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>300</v>
+      </c>
+      <c r="E4" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1148.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>300</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-848.5</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>300</v>
+      </c>
+      <c r="E5" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1148.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>355</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-793.5</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>t1-&gt;t10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>355</v>
+      </c>
+      <c r="E6" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1203.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>300</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-903.5</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>t10-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>300</v>
+      </c>
+      <c r="E7" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1148.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>300</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-848.5</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>300</v>
+      </c>
+      <c r="E8" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1148.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>400</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-748.5</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>400</v>
+      </c>
+      <c r="E9" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1248.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>400</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-848.5</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>400</v>
+      </c>
+      <c r="E10" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1248.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>377.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-871</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>377.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1226</v>
+      </c>
+      <c r="G11" t="n">
+        <v>417.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-808.5</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>t6-&gt;t7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>417.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1266</v>
+      </c>
+      <c r="G12" t="n">
+        <v>417.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-848.5</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>t7-&gt;t8</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>417.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>848.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1266</v>
+      </c>
+      <c r="G13" t="n">
+        <v>377.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-888.5</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>t8-&gt;t9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>德智高新</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>153</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>153</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-153</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>153</v>
+      </c>
+      <c r="H15" t="n">
+        <v>153</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>陆宇君</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>87</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>87</v>
+      </c>
+      <c r="G16" t="n">
+        <v>87</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>已合并</t>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>60</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>60</v>
+      </c>
+      <c r="G17" t="n">
+        <v>60</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>三合融创</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="H18" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>t1-&gt;t10</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>153</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>153</v>
+      </c>
+      <c r="G19" t="n">
+        <v>130.576</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-22.424</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>t1-&gt;t10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>陆宇君</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>87</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>87</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-87</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>t1-&gt;t10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>60</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>60</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-60</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>t1-&gt;t10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>三合融创</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-224.424</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>t10-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>卢娇娇</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>75</v>
+      </c>
+      <c r="H23" t="n">
+        <v>75</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>t10-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>130.576</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>130.576</v>
+      </c>
+      <c r="G24" t="n">
+        <v>90</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-40.576</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>t10-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>陆宇君</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>105</v>
+      </c>
+      <c r="H25" t="n">
+        <v>105</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>t10-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>30</v>
+      </c>
+      <c r="H26" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>t10-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>卢娇娇</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>75</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>75</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-75</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>90</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>90</v>
+      </c>
+      <c r="G28" t="n">
+        <v>75</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-15</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>王洪波</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>陆宇君</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>105</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>105</v>
+      </c>
+      <c r="G30" t="n">
+        <v>105</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>30</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>30</v>
+      </c>
+      <c r="G31" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>75</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>75</v>
+      </c>
+      <c r="G32" t="n">
+        <v>85</v>
+      </c>
+      <c r="H32" t="n">
+        <v>10</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>王洪波</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>55</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>陆宇君</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>105</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>105</v>
+      </c>
+      <c r="G34" t="n">
+        <v>140</v>
+      </c>
+      <c r="H34" t="n">
+        <v>35</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>85</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>85</v>
+      </c>
+      <c r="G36" t="n">
+        <v>225</v>
+      </c>
+      <c r="H36" t="n">
+        <v>140</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>王洪波</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="G37" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>陆宇君</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>140</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>140</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-140</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G39" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>三合融创</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>130</v>
+      </c>
+      <c r="H40" t="n">
+        <v>130</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>225</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>225</v>
+      </c>
+      <c r="G41" t="n">
+        <v>225</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>王洪波</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-152.5</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G43" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>三合融创</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>130</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>130</v>
+      </c>
+      <c r="G44" t="n">
+        <v>130</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>t6-&gt;t7</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>225</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>225</v>
+      </c>
+      <c r="G45" t="n">
+        <v>225</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>t6-&gt;t7</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G46" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>t6-&gt;t7</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>黄晓彬</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>40</v>
+      </c>
+      <c r="H47" t="n">
+        <v>40</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>t6-&gt;t7</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>三合融创</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>130</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>130</v>
+      </c>
+      <c r="G48" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="H48" t="n">
+        <v>94.42400000000001</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>t7-&gt;t8</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>225</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>225</v>
+      </c>
+      <c r="G49" t="n">
+        <v>130.576</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-94.42400000000001</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>t7-&gt;t8</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G50" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>t7-&gt;t8</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>黄晓彬</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>40</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>40</v>
+      </c>
+      <c r="G51" t="n">
+        <v>40</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>t7-&gt;t8</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>三合融创</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="G52" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>t8-&gt;t9</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>130.576</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>130.576</v>
+      </c>
+      <c r="G53" t="n">
+        <v>130.576</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>t8-&gt;t9</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G54" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>t8-&gt;t9</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>黄晓彬</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>40</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>40</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-40</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>t8-&gt;t9</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>3股东</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>t0比例合计71.21%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>3股东</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>t1比例合计71.21%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>4股东</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>t2比例合计96.21%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>4股东</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>t3比例合计103.71%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>4股东</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>t4比例合计103.71%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>3股东</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>t5比例合计103.50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>3股东</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>t6比例合计71.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>4股东</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>t7比例合计80.09%</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>4股东</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>t8比例合计80.09%</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>3股东</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>t9比例合计71.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2股东</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>t10比例合计51.00%</t>
         </is>
       </c>
     </row>
